--- a/12619779.xlsx
+++ b/12619779.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -421,29 +421,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2104,48 +2082,96 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="A29" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B29" s="14">
+        <v>390</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>30</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" ref="I29:I30" si="8">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <v>950</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" ref="J29:J30" si="9">IF(I29="","",1440-I29)</f>
+        <v>490</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="A30" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B30" s="14">
+        <v>390</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" si="8"/>
+        <v>690</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="9"/>
+        <v>750</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13"/>
@@ -2553,11 +2579,11 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" ref="I49:I112" si="8">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <f t="shared" ref="I49:I112" si="10">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
-        <f t="shared" ref="J49:J112" si="9">IF(I49="","",1440-I49)</f>
+        <f t="shared" ref="J49:J112" si="11">IF(I49="","",1440-I49)</f>
         <v/>
       </c>
       <c r="K49" s="16"/>
@@ -2575,11 +2601,11 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K50" s="16"/>
@@ -2597,11 +2623,11 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K51" s="16"/>
@@ -2619,11 +2645,11 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K52" s="16"/>
@@ -2641,11 +2667,11 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K53" s="16"/>
@@ -2663,11 +2689,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -2685,11 +2711,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -2707,11 +2733,11 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K56" s="16"/>
@@ -2729,11 +2755,11 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K57" s="16"/>
@@ -2751,11 +2777,11 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K58" s="16"/>
@@ -2773,11 +2799,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -2795,11 +2821,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2817,11 +2843,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2839,11 +2865,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2861,11 +2887,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2883,11 +2909,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2905,11 +2931,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -2927,11 +2953,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -2949,11 +2975,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -2971,11 +2997,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -2993,11 +3019,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3015,11 +3041,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3037,11 +3063,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3059,11 +3085,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3081,11 +3107,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3103,11 +3129,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3125,11 +3151,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3147,11 +3173,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3169,11 +3195,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3191,11 +3217,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3213,11 +3239,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3235,11 +3261,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3257,11 +3283,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3279,11 +3305,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3301,11 +3327,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3323,11 +3349,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3345,11 +3371,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3367,11 +3393,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3389,11 +3415,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3411,11 +3437,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3433,11 +3459,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3455,11 +3481,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3477,11 +3503,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3499,11 +3525,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3521,11 +3547,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3543,11 +3569,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3565,11 +3591,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3587,11 +3613,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3609,11 +3635,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3631,11 +3657,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3653,11 +3679,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3675,11 +3701,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3697,11 +3723,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3719,11 +3745,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3741,11 +3767,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3763,11 +3789,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3785,11 +3811,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3807,11 +3833,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3829,11 +3855,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3851,11 +3877,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3873,11 +3899,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3895,11 +3921,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3917,11 +3943,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3939,11 +3965,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3961,11 +3987,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" ref="I113:I176" si="10">IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
+        <f t="shared" ref="I113:I176" si="12">IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" ref="J113:J176" si="11">IF(I113="","",1440-I113)</f>
+        <f t="shared" ref="J113:J176" si="13">IF(I113="","",1440-I113)</f>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3983,11 +4009,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4005,11 +4031,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4027,11 +4053,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4049,11 +4075,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4071,11 +4097,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4093,11 +4119,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4115,11 +4141,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4137,11 +4163,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4159,11 +4185,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4181,11 +4207,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4203,11 +4229,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4225,11 +4251,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4247,11 +4273,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4269,11 +4295,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4291,11 +4317,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4313,11 +4339,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4335,11 +4361,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4357,11 +4383,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4379,11 +4405,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4401,11 +4427,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4423,11 +4449,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4445,11 +4471,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4467,11 +4493,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4489,11 +4515,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4511,11 +4537,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4533,11 +4559,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4555,11 +4581,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4577,11 +4603,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4599,11 +4625,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4621,11 +4647,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4643,11 +4669,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4665,11 +4691,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4687,11 +4713,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4709,11 +4735,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4731,11 +4757,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4753,11 +4779,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4775,11 +4801,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4797,11 +4823,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4819,11 +4845,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4841,11 +4867,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4863,11 +4889,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4885,11 +4911,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4907,11 +4933,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4929,11 +4955,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4951,11 +4977,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4973,11 +4999,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4995,11 +5021,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5017,11 +5043,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5039,11 +5065,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5061,11 +5087,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5083,11 +5109,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5105,11 +5131,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5127,11 +5153,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5149,11 +5175,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5171,11 +5197,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5193,11 +5219,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5215,11 +5241,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5237,11 +5263,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5259,11 +5285,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5281,11 +5307,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5303,11 +5329,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5325,11 +5351,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5347,11 +5373,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5369,11 +5395,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" ref="I177:I240" si="12">IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
+        <f t="shared" ref="I177:I240" si="14">IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" ref="J177:J240" si="13">IF(I177="","",1440-I177)</f>
+        <f t="shared" ref="J177:J240" si="15">IF(I177="","",1440-I177)</f>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5391,11 +5417,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5413,11 +5439,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5435,11 +5461,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5457,11 +5483,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5479,11 +5505,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5501,11 +5527,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5523,11 +5549,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5545,11 +5571,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5567,11 +5593,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5589,11 +5615,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5611,11 +5637,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5633,11 +5659,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5655,11 +5681,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5677,11 +5703,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5699,11 +5725,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5721,11 +5747,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5743,11 +5769,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5765,11 +5791,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5787,11 +5813,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5809,11 +5835,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5831,11 +5857,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5853,11 +5879,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5875,11 +5901,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5897,11 +5923,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5919,11 +5945,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5941,11 +5967,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5963,11 +5989,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5985,11 +6011,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6007,11 +6033,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6029,11 +6055,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6051,11 +6077,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6073,11 +6099,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6095,11 +6121,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6117,11 +6143,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6139,11 +6165,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6161,11 +6187,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6183,11 +6209,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6205,11 +6231,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6227,11 +6253,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6249,11 +6275,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6271,11 +6297,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6293,11 +6319,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6315,11 +6341,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6337,11 +6363,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6359,11 +6385,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6381,11 +6407,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6403,11 +6429,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6425,11 +6451,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6447,11 +6473,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6469,11 +6495,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6491,11 +6517,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6513,11 +6539,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6535,11 +6561,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6557,11 +6583,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6579,11 +6605,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6601,11 +6627,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6623,11 +6649,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6645,11 +6671,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6667,11 +6693,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6689,11 +6715,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6711,11 +6737,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6733,11 +6759,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6755,11 +6781,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6777,11 +6803,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" ref="I241:I304" si="14">IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
+        <f t="shared" ref="I241:I304" si="16">IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" ref="J241:J304" si="15">IF(I241="","",1440-I241)</f>
+        <f t="shared" ref="J241:J304" si="17">IF(I241="","",1440-I241)</f>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6799,11 +6825,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6821,11 +6847,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6843,11 +6869,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6865,11 +6891,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6887,11 +6913,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6909,11 +6935,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6931,11 +6957,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6953,11 +6979,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6975,11 +7001,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6997,11 +7023,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7019,11 +7045,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7041,11 +7067,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7063,11 +7089,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7085,11 +7111,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7107,11 +7133,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7129,11 +7155,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7151,11 +7177,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7173,11 +7199,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7195,11 +7221,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7217,11 +7243,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7239,11 +7265,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7261,11 +7287,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7283,11 +7309,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7305,11 +7331,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7327,11 +7353,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7349,11 +7375,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7371,11 +7397,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7393,11 +7419,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7415,11 +7441,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7437,11 +7463,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7459,11 +7485,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7481,11 +7507,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7503,11 +7529,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7525,11 +7551,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7547,11 +7573,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7569,11 +7595,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7591,11 +7617,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7613,11 +7639,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7635,11 +7661,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7657,11 +7683,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7679,11 +7705,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7701,11 +7727,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7723,11 +7749,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7745,11 +7771,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7767,11 +7793,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7789,11 +7815,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7811,11 +7837,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7833,11 +7859,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7855,11 +7881,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7877,11 +7903,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7899,11 +7925,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7921,11 +7947,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7943,11 +7969,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7965,11 +7991,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7987,11 +8013,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8009,11 +8035,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8031,11 +8057,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8053,11 +8079,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8075,11 +8101,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8097,11 +8123,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8119,11 +8145,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8141,11 +8167,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8163,11 +8189,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8185,11 +8211,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" ref="I305:I368" si="16">IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
+        <f t="shared" ref="I305:I368" si="18">IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" ref="J305:J368" si="17">IF(I305="","",1440-I305)</f>
+        <f t="shared" ref="J305:J368" si="19">IF(I305="","",1440-I305)</f>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8207,11 +8233,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8229,11 +8255,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8251,11 +8277,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8273,11 +8299,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8295,11 +8321,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8317,11 +8343,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8339,11 +8365,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8361,11 +8387,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8383,11 +8409,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8405,11 +8431,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8427,11 +8453,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8449,11 +8475,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8471,11 +8497,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8493,11 +8519,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8515,11 +8541,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8537,11 +8563,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8559,11 +8585,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8581,11 +8607,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8603,11 +8629,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8625,11 +8651,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8647,11 +8673,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8669,11 +8695,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8691,11 +8717,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8713,11 +8739,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8735,11 +8761,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8757,11 +8783,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8779,11 +8805,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8801,11 +8827,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8823,11 +8849,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8845,11 +8871,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8867,11 +8893,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8889,11 +8915,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8911,11 +8937,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8933,11 +8959,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8955,11 +8981,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8977,11 +9003,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8999,11 +9025,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9021,11 +9047,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9043,11 +9069,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9065,11 +9091,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9087,11 +9113,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9109,11 +9135,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9131,11 +9157,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9153,11 +9179,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9175,11 +9201,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9197,11 +9223,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9219,11 +9245,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9241,11 +9267,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9263,11 +9289,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9285,11 +9311,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9307,11 +9333,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9329,11 +9355,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9351,11 +9377,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9373,11 +9399,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9395,11 +9421,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9417,11 +9443,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9439,11 +9465,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9461,11 +9487,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9483,11 +9509,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9505,11 +9531,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9527,11 +9553,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9549,11 +9575,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9571,11 +9597,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9593,11 +9619,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" ref="I369:I380" si="18">IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
+        <f t="shared" ref="I369:I380" si="20">IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" ref="J369:J380" si="19">IF(I369="","",1440-I369)</f>
+        <f t="shared" ref="J369:J380" si="21">IF(I369="","",1440-I369)</f>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9615,11 +9641,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9637,11 +9663,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9659,11 +9685,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9681,11 +9707,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9703,11 +9729,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9725,11 +9751,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9747,11 +9773,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9769,11 +9795,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9791,11 +9817,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9813,11 +9839,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9835,11 +9861,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9857,7 +9883,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J380">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12619779.xlsx
+++ b/12619779.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2107,11 +2107,11 @@
         <v>30</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" ref="I29:I30" si="8">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <f t="shared" ref="I29:I32" si="8">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
         <v>950</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" ref="J29:J30" si="9">IF(I29="","",1440-I29)</f>
+        <f t="shared" ref="J29:J32" si="9">IF(I29="","",1440-I29)</f>
         <v>490</v>
       </c>
       <c r="K29" s="16" t="s">
@@ -2174,48 +2174,96 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="A31" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="14">
+        <v>390</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>90</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="8"/>
+        <v>690</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="9"/>
+        <v>750</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="A32" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="14">
+        <v>390</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>90</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="8"/>
+        <v>830</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="9"/>
+        <v>610</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13"/>

--- a/12619779.xlsx
+++ b/12619779.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2107,11 +2107,11 @@
         <v>30</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" ref="I29:I32" si="8">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <f t="shared" ref="I29:I35" si="8">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
         <v>950</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" ref="J29:J32" si="9">IF(I29="","",1440-I29)</f>
+        <f t="shared" ref="J29:J35" si="9">IF(I29="","",1440-I29)</f>
         <v>490</v>
       </c>
       <c r="K29" s="16" t="s">
@@ -2266,70 +2266,142 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="A33" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="14">
+        <v>390</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>90</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="8"/>
+        <v>910</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="9"/>
+        <v>530</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="A34" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B34" s="14">
+        <v>390</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="8"/>
+        <v>900</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="9"/>
+        <v>540</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="A35" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="14">
+        <v>390</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="8"/>
+        <v>1080</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="9"/>
+        <v>360</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="13"/>

--- a/12619779.xlsx
+++ b/12619779.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2404,92 +2404,188 @@
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="A36" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B36" s="14">
+        <v>390</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>30</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" ref="I36:I39" si="10">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>950</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" ref="J36:J39" si="11">IF(I36="","",1440-I36)</f>
+        <v>490</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="A37" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B37" s="14">
+        <v>390</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>90</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="10"/>
+        <v>690</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="11"/>
+        <v>750</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="A38" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B38" s="14">
+        <v>390</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>90</v>
+      </c>
+      <c r="E38" s="14">
+        <v>90</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>90</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="10"/>
+        <v>690</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="11"/>
+        <v>750</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B39" s="14">
+        <v>390</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>90</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>90</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="10"/>
+        <v>660</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="11"/>
+        <v>780</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13"/>
@@ -2699,11 +2795,11 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" ref="I49:I112" si="10">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <f t="shared" ref="I49:I112" si="12">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
-        <f t="shared" ref="J49:J112" si="11">IF(I49="","",1440-I49)</f>
+        <f t="shared" ref="J49:J112" si="13">IF(I49="","",1440-I49)</f>
         <v/>
       </c>
       <c r="K49" s="16"/>
@@ -2721,11 +2817,11 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K50" s="16"/>
@@ -2743,11 +2839,11 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K51" s="16"/>
@@ -2765,11 +2861,11 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K52" s="16"/>
@@ -2787,11 +2883,11 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K53" s="16"/>
@@ -2809,11 +2905,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -2831,11 +2927,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -2853,11 +2949,11 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K56" s="16"/>
@@ -2875,11 +2971,11 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K57" s="16"/>
@@ -2897,11 +2993,11 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K58" s="16"/>
@@ -2919,11 +3015,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -2941,11 +3037,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2963,11 +3059,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2985,11 +3081,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -3007,11 +3103,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -3029,11 +3125,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -3051,11 +3147,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -3073,11 +3169,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -3095,11 +3191,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -3117,11 +3213,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3139,11 +3235,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3161,11 +3257,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3183,11 +3279,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3205,11 +3301,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3227,11 +3323,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3249,11 +3345,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3271,11 +3367,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3293,11 +3389,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3315,11 +3411,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3337,11 +3433,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3359,11 +3455,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3381,11 +3477,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3403,11 +3499,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3425,11 +3521,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3447,11 +3543,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3469,11 +3565,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3491,11 +3587,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3513,11 +3609,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3535,11 +3631,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3557,11 +3653,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3579,11 +3675,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3601,11 +3697,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3623,11 +3719,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3645,11 +3741,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3667,11 +3763,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3689,11 +3785,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3711,11 +3807,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3733,11 +3829,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3755,11 +3851,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3777,11 +3873,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3799,11 +3895,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3821,11 +3917,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3843,11 +3939,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3865,11 +3961,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3887,11 +3983,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3909,11 +4005,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3931,11 +4027,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3953,11 +4049,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3975,11 +4071,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3997,11 +4093,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4019,11 +4115,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4041,11 +4137,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4063,11 +4159,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4085,11 +4181,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4107,11 +4203,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" ref="I113:I176" si="12">IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
+        <f t="shared" ref="I113:I176" si="14">IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" ref="J113:J176" si="13">IF(I113="","",1440-I113)</f>
+        <f t="shared" ref="J113:J176" si="15">IF(I113="","",1440-I113)</f>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4129,11 +4225,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4151,11 +4247,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4173,11 +4269,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4195,11 +4291,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4217,11 +4313,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4239,11 +4335,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4261,11 +4357,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4283,11 +4379,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4305,11 +4401,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4327,11 +4423,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4349,11 +4445,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4371,11 +4467,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4393,11 +4489,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4415,11 +4511,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4437,11 +4533,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4459,11 +4555,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4481,11 +4577,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4503,11 +4599,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4525,11 +4621,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4547,11 +4643,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4569,11 +4665,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4591,11 +4687,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4613,11 +4709,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4635,11 +4731,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4657,11 +4753,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4679,11 +4775,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4701,11 +4797,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4723,11 +4819,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4745,11 +4841,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4767,11 +4863,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4789,11 +4885,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4811,11 +4907,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4833,11 +4929,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4855,11 +4951,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4877,11 +4973,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4899,11 +4995,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4921,11 +5017,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4943,11 +5039,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4965,11 +5061,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4987,11 +5083,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5009,11 +5105,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5031,11 +5127,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5053,11 +5149,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5075,11 +5171,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5097,11 +5193,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5119,11 +5215,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5141,11 +5237,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5163,11 +5259,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5185,11 +5281,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5207,11 +5303,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5229,11 +5325,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5251,11 +5347,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5273,11 +5369,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5295,11 +5391,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5317,11 +5413,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5339,11 +5435,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5361,11 +5457,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5383,11 +5479,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5405,11 +5501,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5427,11 +5523,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5449,11 +5545,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5471,11 +5567,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5493,11 +5589,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5515,11 +5611,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" ref="I177:I240" si="14">IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
+        <f t="shared" ref="I177:I240" si="16">IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" ref="J177:J240" si="15">IF(I177="","",1440-I177)</f>
+        <f t="shared" ref="J177:J240" si="17">IF(I177="","",1440-I177)</f>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5537,11 +5633,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5559,11 +5655,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5581,11 +5677,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5603,11 +5699,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5625,11 +5721,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5647,11 +5743,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5669,11 +5765,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5691,11 +5787,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5713,11 +5809,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5735,11 +5831,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5757,11 +5853,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5779,11 +5875,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5801,11 +5897,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5823,11 +5919,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5845,11 +5941,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5867,11 +5963,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5889,11 +5985,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5911,11 +6007,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5933,11 +6029,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5955,11 +6051,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5977,11 +6073,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5999,11 +6095,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6021,11 +6117,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6043,11 +6139,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6065,11 +6161,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6087,11 +6183,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6109,11 +6205,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6131,11 +6227,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6153,11 +6249,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6175,11 +6271,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6197,11 +6293,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6219,11 +6315,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6241,11 +6337,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6263,11 +6359,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6285,11 +6381,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6307,11 +6403,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6329,11 +6425,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6351,11 +6447,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6373,11 +6469,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6395,11 +6491,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6417,11 +6513,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6439,11 +6535,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6461,11 +6557,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6483,11 +6579,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6505,11 +6601,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6527,11 +6623,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6549,11 +6645,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6571,11 +6667,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6593,11 +6689,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6615,11 +6711,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6637,11 +6733,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6659,11 +6755,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6681,11 +6777,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6703,11 +6799,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6725,11 +6821,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6747,11 +6843,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6769,11 +6865,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6791,11 +6887,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6813,11 +6909,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6835,11 +6931,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6857,11 +6953,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6879,11 +6975,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6901,11 +6997,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6923,11 +7019,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" ref="I241:I304" si="16">IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
+        <f t="shared" ref="I241:I304" si="18">IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" ref="J241:J304" si="17">IF(I241="","",1440-I241)</f>
+        <f t="shared" ref="J241:J304" si="19">IF(I241="","",1440-I241)</f>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6945,11 +7041,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6967,11 +7063,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6989,11 +7085,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7011,11 +7107,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7033,11 +7129,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7055,11 +7151,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7077,11 +7173,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7099,11 +7195,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7121,11 +7217,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7143,11 +7239,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7165,11 +7261,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7187,11 +7283,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7209,11 +7305,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7231,11 +7327,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7253,11 +7349,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7275,11 +7371,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7297,11 +7393,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7319,11 +7415,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7341,11 +7437,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7363,11 +7459,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7385,11 +7481,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7407,11 +7503,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7429,11 +7525,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7451,11 +7547,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7473,11 +7569,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7495,11 +7591,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7517,11 +7613,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7539,11 +7635,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7561,11 +7657,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7583,11 +7679,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7605,11 +7701,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7627,11 +7723,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7649,11 +7745,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7671,11 +7767,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7693,11 +7789,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7715,11 +7811,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7737,11 +7833,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7759,11 +7855,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7781,11 +7877,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7803,11 +7899,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7825,11 +7921,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7847,11 +7943,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7869,11 +7965,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7891,11 +7987,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7913,11 +8009,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7935,11 +8031,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7957,11 +8053,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7979,11 +8075,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8001,11 +8097,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8023,11 +8119,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8045,11 +8141,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8067,11 +8163,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8089,11 +8185,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8111,11 +8207,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8133,11 +8229,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8155,11 +8251,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8177,11 +8273,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8199,11 +8295,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8221,11 +8317,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8243,11 +8339,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8265,11 +8361,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8287,11 +8383,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8309,11 +8405,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8331,11 +8427,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" ref="I305:I368" si="18">IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
+        <f t="shared" ref="I305:I368" si="20">IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" ref="J305:J368" si="19">IF(I305="","",1440-I305)</f>
+        <f t="shared" ref="J305:J368" si="21">IF(I305="","",1440-I305)</f>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8353,11 +8449,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8375,11 +8471,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8397,11 +8493,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8419,11 +8515,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8441,11 +8537,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8463,11 +8559,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8485,11 +8581,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8507,11 +8603,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8529,11 +8625,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8551,11 +8647,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8573,11 +8669,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8595,11 +8691,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8617,11 +8713,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8639,11 +8735,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8661,11 +8757,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8683,11 +8779,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8705,11 +8801,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8727,11 +8823,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8749,11 +8845,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8771,11 +8867,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8793,11 +8889,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8815,11 +8911,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8837,11 +8933,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8859,11 +8955,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8881,11 +8977,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8903,11 +8999,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8925,11 +9021,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8947,11 +9043,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8969,11 +9065,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8991,11 +9087,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9013,11 +9109,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9035,11 +9131,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9057,11 +9153,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9079,11 +9175,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9101,11 +9197,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9123,11 +9219,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9145,11 +9241,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9167,11 +9263,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9189,11 +9285,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9211,11 +9307,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9233,11 +9329,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9255,11 +9351,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9277,11 +9373,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9299,11 +9395,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9321,11 +9417,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9343,11 +9439,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9365,11 +9461,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9387,11 +9483,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9409,11 +9505,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9431,11 +9527,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9453,11 +9549,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9475,11 +9571,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9497,11 +9593,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9519,11 +9615,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9541,11 +9637,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9563,11 +9659,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9585,11 +9681,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9607,11 +9703,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9629,11 +9725,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9651,11 +9747,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9673,11 +9769,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9695,11 +9791,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9717,11 +9813,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9739,11 +9835,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" ref="I369:I380" si="20">IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
+        <f t="shared" ref="I369:I380" si="22">IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" ref="J369:J380" si="21">IF(I369="","",1440-I369)</f>
+        <f t="shared" ref="J369:J380" si="23">IF(I369="","",1440-I369)</f>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9761,11 +9857,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9783,11 +9879,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9805,11 +9901,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9827,11 +9923,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9849,11 +9945,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9871,11 +9967,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9893,11 +9989,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9915,11 +10011,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9937,11 +10033,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9959,11 +10055,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9981,11 +10077,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K380" s="16"/>

--- a/12619779.xlsx
+++ b/12619779.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="August" sheetId="2" r:id="rId2"/>
-    <sheet name="September" sheetId="3" r:id="rId3"/>
+    <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725" iterateDelta="1E-4"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -234,9 +233,6 @@
   <si>
     <t xml:space="preserve">Enjoyable </t>
   </si>
-  <si>
-    <t xml:space="preserve">                               September</t>
-  </si>
 </sst>
 </file>
 
@@ -400,51 +396,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10189,7 +10141,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J381">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10210,9390 +10162,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N382"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="20.6328125" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" customWidth="1"/>
-    <col min="5" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="15">
-        <v>12619779</v>
-      </c>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" spans="1:14" ht="42">
-      <c r="A5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="8">
-        <v>46266</v>
-      </c>
-      <c r="B6" s="9">
-        <v>390</v>
-      </c>
-      <c r="C6" s="9">
-        <v>30</v>
-      </c>
-      <c r="D6" s="9">
-        <v>60</v>
-      </c>
-      <c r="E6" s="9">
-        <v>90</v>
-      </c>
-      <c r="F6" s="9">
-        <v>300</v>
-      </c>
-      <c r="G6" s="9">
-        <v>6</v>
-      </c>
-      <c r="H6" s="9">
-        <v>30</v>
-      </c>
-      <c r="I6" s="10">
-        <f t="shared" ref="I6:I26" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>900</v>
-      </c>
-      <c r="J6" s="10">
-        <f t="shared" ref="J6:J26" si="1">IF(I6="","",1440-I6)</f>
-        <v>540</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="8">
-        <v>46267</v>
-      </c>
-      <c r="B7" s="9">
-        <v>390</v>
-      </c>
-      <c r="C7" s="9">
-        <v>30</v>
-      </c>
-      <c r="D7" s="9">
-        <v>90</v>
-      </c>
-      <c r="E7" s="9">
-        <v>90</v>
-      </c>
-      <c r="F7" s="9">
-        <v>350</v>
-      </c>
-      <c r="G7" s="9">
-        <v>7</v>
-      </c>
-      <c r="H7" s="9">
-        <v>60</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" si="0"/>
-        <v>1010</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" si="1"/>
-        <v>430</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="8">
-        <v>46268</v>
-      </c>
-      <c r="B8" s="9">
-        <v>390</v>
-      </c>
-      <c r="C8" s="9">
-        <v>30</v>
-      </c>
-      <c r="D8" s="9">
-        <v>60</v>
-      </c>
-      <c r="E8" s="9">
-        <v>90</v>
-      </c>
-      <c r="F8" s="9">
-        <v>350</v>
-      </c>
-      <c r="G8" s="9">
-        <v>7</v>
-      </c>
-      <c r="H8" s="9">
-        <v>30</v>
-      </c>
-      <c r="I8" s="10">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="8">
-        <v>46269</v>
-      </c>
-      <c r="B9" s="9">
-        <v>390</v>
-      </c>
-      <c r="C9" s="9">
-        <v>30</v>
-      </c>
-      <c r="D9" s="9">
-        <v>120</v>
-      </c>
-      <c r="E9" s="9">
-        <v>90</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>60</v>
-      </c>
-      <c r="I9" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J9" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B10" s="9">
-        <v>390</v>
-      </c>
-      <c r="C10" s="9">
-        <v>30</v>
-      </c>
-      <c r="D10" s="9">
-        <v>90</v>
-      </c>
-      <c r="E10" s="9">
-        <v>90</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>90</v>
-      </c>
-      <c r="I10" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J10" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="8">
-        <v>46271</v>
-      </c>
-      <c r="B11" s="9">
-        <v>390</v>
-      </c>
-      <c r="C11" s="9">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9">
-        <v>90</v>
-      </c>
-      <c r="E11" s="9">
-        <v>90</v>
-      </c>
-      <c r="F11" s="9">
-        <v>250</v>
-      </c>
-      <c r="G11" s="9">
-        <v>5</v>
-      </c>
-      <c r="H11" s="9">
-        <v>30</v>
-      </c>
-      <c r="I11" s="10">
-        <f t="shared" si="0"/>
-        <v>880</v>
-      </c>
-      <c r="J11" s="10">
-        <f t="shared" si="1"/>
-        <v>560</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B12" s="9">
-        <v>390</v>
-      </c>
-      <c r="C12" s="9">
-        <v>30</v>
-      </c>
-      <c r="D12" s="9">
-        <v>90</v>
-      </c>
-      <c r="E12" s="9">
-        <v>90</v>
-      </c>
-      <c r="F12" s="9">
-        <v>250</v>
-      </c>
-      <c r="G12" s="9">
-        <v>5</v>
-      </c>
-      <c r="H12" s="9">
-        <v>60</v>
-      </c>
-      <c r="I12" s="10">
-        <f t="shared" si="0"/>
-        <v>910</v>
-      </c>
-      <c r="J12" s="10">
-        <f t="shared" si="1"/>
-        <v>530</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B13" s="9">
-        <v>390</v>
-      </c>
-      <c r="C13" s="9">
-        <v>30</v>
-      </c>
-      <c r="D13" s="9">
-        <v>60</v>
-      </c>
-      <c r="E13" s="9">
-        <v>90</v>
-      </c>
-      <c r="F13" s="9">
-        <v>300</v>
-      </c>
-      <c r="G13" s="9">
-        <v>6</v>
-      </c>
-      <c r="H13" s="9">
-        <v>30</v>
-      </c>
-      <c r="I13" s="10">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J13" s="10">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B14" s="9">
-        <v>390</v>
-      </c>
-      <c r="C14" s="9">
-        <v>30</v>
-      </c>
-      <c r="D14" s="9">
-        <v>90</v>
-      </c>
-      <c r="E14" s="9">
-        <v>90</v>
-      </c>
-      <c r="F14" s="9">
-        <v>100</v>
-      </c>
-      <c r="G14" s="9">
-        <v>2</v>
-      </c>
-      <c r="H14" s="9">
-        <v>180</v>
-      </c>
-      <c r="I14" s="10">
-        <f t="shared" si="0"/>
-        <v>880</v>
-      </c>
-      <c r="J14" s="10">
-        <f t="shared" si="1"/>
-        <v>560</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B15" s="9">
-        <v>390</v>
-      </c>
-      <c r="C15" s="9">
-        <v>30</v>
-      </c>
-      <c r="D15" s="9">
-        <v>60</v>
-      </c>
-      <c r="E15" s="9">
-        <v>90</v>
-      </c>
-      <c r="F15" s="9">
-        <v>350</v>
-      </c>
-      <c r="G15" s="9">
-        <v>7</v>
-      </c>
-      <c r="H15" s="9">
-        <v>30</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J15" s="10">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B16" s="9">
-        <v>390</v>
-      </c>
-      <c r="C16" s="9">
-        <v>30</v>
-      </c>
-      <c r="D16" s="9">
-        <v>120</v>
-      </c>
-      <c r="E16" s="9">
-        <v>90</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>60</v>
-      </c>
-      <c r="I16" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J16" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="8">
-        <v>46277</v>
-      </c>
-      <c r="B17" s="9">
-        <v>390</v>
-      </c>
-      <c r="C17" s="9">
-        <v>30</v>
-      </c>
-      <c r="D17" s="9">
-        <v>90</v>
-      </c>
-      <c r="E17" s="9">
-        <v>90</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>90</v>
-      </c>
-      <c r="I17" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J17" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="8">
-        <v>46278</v>
-      </c>
-      <c r="B18" s="9">
-        <v>390</v>
-      </c>
-      <c r="C18" s="9">
-        <v>30</v>
-      </c>
-      <c r="D18" s="9">
-        <v>90</v>
-      </c>
-      <c r="E18" s="9">
-        <v>90</v>
-      </c>
-      <c r="F18" s="9">
-        <v>200</v>
-      </c>
-      <c r="G18" s="9">
-        <v>4</v>
-      </c>
-      <c r="H18" s="9">
-        <v>30</v>
-      </c>
-      <c r="I18" s="10">
-        <f t="shared" si="0"/>
-        <v>830</v>
-      </c>
-      <c r="J18" s="10">
-        <f t="shared" si="1"/>
-        <v>610</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="8">
-        <v>46279</v>
-      </c>
-      <c r="B19" s="9">
-        <v>390</v>
-      </c>
-      <c r="C19" s="9">
-        <v>30</v>
-      </c>
-      <c r="D19" s="9">
-        <v>90</v>
-      </c>
-      <c r="E19" s="9">
-        <v>90</v>
-      </c>
-      <c r="F19" s="9">
-        <v>250</v>
-      </c>
-      <c r="G19" s="9">
-        <v>5</v>
-      </c>
-      <c r="H19" s="9">
-        <v>60</v>
-      </c>
-      <c r="I19" s="10">
-        <f t="shared" si="0"/>
-        <v>910</v>
-      </c>
-      <c r="J19" s="10">
-        <f t="shared" si="1"/>
-        <v>530</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B20" s="9">
-        <v>390</v>
-      </c>
-      <c r="C20" s="9">
-        <v>30</v>
-      </c>
-      <c r="D20" s="9">
-        <v>60</v>
-      </c>
-      <c r="E20" s="9">
-        <v>90</v>
-      </c>
-      <c r="F20" s="9">
-        <v>300</v>
-      </c>
-      <c r="G20" s="9">
-        <v>5</v>
-      </c>
-      <c r="H20" s="9">
-        <v>30</v>
-      </c>
-      <c r="I20" s="10">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J20" s="10">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="8">
-        <v>46281</v>
-      </c>
-      <c r="B21" s="9">
-        <v>390</v>
-      </c>
-      <c r="C21" s="9">
-        <v>30</v>
-      </c>
-      <c r="D21" s="9">
-        <v>90</v>
-      </c>
-      <c r="E21" s="9">
-        <v>90</v>
-      </c>
-      <c r="F21" s="9">
-        <v>300</v>
-      </c>
-      <c r="G21" s="9">
-        <v>6</v>
-      </c>
-      <c r="H21" s="9">
-        <v>180</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="0"/>
-        <v>1080</v>
-      </c>
-      <c r="J21" s="10">
-        <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="8">
-        <v>46282</v>
-      </c>
-      <c r="B22" s="9">
-        <v>390</v>
-      </c>
-      <c r="C22" s="9">
-        <v>30</v>
-      </c>
-      <c r="D22" s="9">
-        <v>60</v>
-      </c>
-      <c r="E22" s="9">
-        <v>90</v>
-      </c>
-      <c r="F22" s="9">
-        <v>350</v>
-      </c>
-      <c r="G22" s="9">
-        <v>7</v>
-      </c>
-      <c r="H22" s="9">
-        <v>30</v>
-      </c>
-      <c r="I22" s="10">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J22" s="10">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B23" s="9">
-        <v>390</v>
-      </c>
-      <c r="C23" s="9">
-        <v>30</v>
-      </c>
-      <c r="D23" s="9">
-        <v>120</v>
-      </c>
-      <c r="E23" s="9">
-        <v>90</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>60</v>
-      </c>
-      <c r="I23" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J23" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B24" s="9">
-        <v>390</v>
-      </c>
-      <c r="C24" s="9">
-        <v>30</v>
-      </c>
-      <c r="D24" s="9">
-        <v>90</v>
-      </c>
-      <c r="E24" s="9">
-        <v>90</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>90</v>
-      </c>
-      <c r="I24" s="10">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J24" s="10">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B25" s="9">
-        <v>390</v>
-      </c>
-      <c r="C25" s="9">
-        <v>30</v>
-      </c>
-      <c r="D25" s="9">
-        <v>90</v>
-      </c>
-      <c r="E25" s="9">
-        <v>60</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>90</v>
-      </c>
-      <c r="I25" s="10">
-        <f t="shared" si="0"/>
-        <v>660</v>
-      </c>
-      <c r="J25" s="10">
-        <f t="shared" si="1"/>
-        <v>780</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B26" s="9">
-        <v>390</v>
-      </c>
-      <c r="C26" s="9">
-        <v>30</v>
-      </c>
-      <c r="D26" s="9">
-        <v>60</v>
-      </c>
-      <c r="E26" s="9">
-        <v>60</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>90</v>
-      </c>
-      <c r="I26" s="10">
-        <f t="shared" si="0"/>
-        <v>630</v>
-      </c>
-      <c r="J26" s="10">
-        <f t="shared" si="1"/>
-        <v>810</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B27" s="9">
-        <v>390</v>
-      </c>
-      <c r="C27" s="9">
-        <v>30</v>
-      </c>
-      <c r="D27" s="9">
-        <v>90</v>
-      </c>
-      <c r="E27" s="9">
-        <v>90</v>
-      </c>
-      <c r="F27" s="9">
-        <v>250</v>
-      </c>
-      <c r="G27" s="9">
-        <v>5</v>
-      </c>
-      <c r="H27" s="9">
-        <v>60</v>
-      </c>
-      <c r="I27" s="10">
-        <f t="shared" ref="I27:I69" si="2">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v>910</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" ref="J27:J69" si="3">IF(I27="","",1440-I27)</f>
-        <v>530</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B28" s="9">
-        <v>390</v>
-      </c>
-      <c r="C28" s="9">
-        <v>30</v>
-      </c>
-      <c r="D28" s="9">
-        <v>60</v>
-      </c>
-      <c r="E28" s="9">
-        <v>90</v>
-      </c>
-      <c r="F28" s="9">
-        <v>300</v>
-      </c>
-      <c r="G28" s="9">
-        <v>6</v>
-      </c>
-      <c r="H28" s="9">
-        <v>30</v>
-      </c>
-      <c r="I28" s="10">
-        <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="3"/>
-        <v>540</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B29" s="9">
-        <v>390</v>
-      </c>
-      <c r="C29" s="9">
-        <v>30</v>
-      </c>
-      <c r="D29" s="9">
-        <v>90</v>
-      </c>
-      <c r="E29" s="9">
-        <v>90</v>
-      </c>
-      <c r="F29" s="9">
-        <v>100</v>
-      </c>
-      <c r="G29" s="9">
-        <v>2</v>
-      </c>
-      <c r="H29" s="9">
-        <v>180</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="3"/>
-        <v>560</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B30" s="9">
-        <v>390</v>
-      </c>
-      <c r="C30" s="9">
-        <v>30</v>
-      </c>
-      <c r="D30" s="9">
-        <v>60</v>
-      </c>
-      <c r="E30" s="9">
-        <v>90</v>
-      </c>
-      <c r="F30" s="9">
-        <v>350</v>
-      </c>
-      <c r="G30" s="9">
-        <v>7</v>
-      </c>
-      <c r="H30" s="9">
-        <v>30</v>
-      </c>
-      <c r="I30" s="10">
-        <f t="shared" si="2"/>
-        <v>950</v>
-      </c>
-      <c r="J30" s="10">
-        <f t="shared" si="3"/>
-        <v>490</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B31" s="9">
-        <v>390</v>
-      </c>
-      <c r="C31" s="9">
-        <v>30</v>
-      </c>
-      <c r="D31" s="9">
-        <v>120</v>
-      </c>
-      <c r="E31" s="9">
-        <v>90</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>60</v>
-      </c>
-      <c r="I31" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
-      </c>
-      <c r="J31" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="8">
-        <v>46277</v>
-      </c>
-      <c r="B32" s="9">
-        <v>390</v>
-      </c>
-      <c r="C32" s="9">
-        <v>30</v>
-      </c>
-      <c r="D32" s="9">
-        <v>90</v>
-      </c>
-      <c r="E32" s="9">
-        <v>90</v>
-      </c>
-      <c r="F32" s="9">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>90</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
-      </c>
-      <c r="J32" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="8">
-        <v>46278</v>
-      </c>
-      <c r="B33" s="9">
-        <v>390</v>
-      </c>
-      <c r="C33" s="9">
-        <v>30</v>
-      </c>
-      <c r="D33" s="9">
-        <v>90</v>
-      </c>
-      <c r="E33" s="9">
-        <v>90</v>
-      </c>
-      <c r="F33" s="9">
-        <v>200</v>
-      </c>
-      <c r="G33" s="9">
-        <v>4</v>
-      </c>
-      <c r="H33" s="9">
-        <v>30</v>
-      </c>
-      <c r="I33" s="10">
-        <f t="shared" si="2"/>
-        <v>830</v>
-      </c>
-      <c r="J33" s="10">
-        <f t="shared" si="3"/>
-        <v>610</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="8">
-        <v>46279</v>
-      </c>
-      <c r="B34" s="9">
-        <v>390</v>
-      </c>
-      <c r="C34" s="9">
-        <v>30</v>
-      </c>
-      <c r="D34" s="9">
-        <v>90</v>
-      </c>
-      <c r="E34" s="9">
-        <v>90</v>
-      </c>
-      <c r="F34" s="9">
-        <v>250</v>
-      </c>
-      <c r="G34" s="9">
-        <v>5</v>
-      </c>
-      <c r="H34" s="9">
-        <v>60</v>
-      </c>
-      <c r="I34" s="10">
-        <f t="shared" si="2"/>
-        <v>910</v>
-      </c>
-      <c r="J34" s="10">
-        <f t="shared" si="3"/>
-        <v>530</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B35" s="9">
-        <v>390</v>
-      </c>
-      <c r="C35" s="9">
-        <v>30</v>
-      </c>
-      <c r="D35" s="9">
-        <v>60</v>
-      </c>
-      <c r="E35" s="9">
-        <v>90</v>
-      </c>
-      <c r="F35" s="9">
-        <v>300</v>
-      </c>
-      <c r="G35" s="9">
-        <v>5</v>
-      </c>
-      <c r="H35" s="9">
-        <v>30</v>
-      </c>
-      <c r="I35" s="10">
-        <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-      <c r="J35" s="10">
-        <f t="shared" si="3"/>
-        <v>540</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="8">
-        <v>46281</v>
-      </c>
-      <c r="B36" s="9">
-        <v>390</v>
-      </c>
-      <c r="C36" s="9">
-        <v>30</v>
-      </c>
-      <c r="D36" s="9">
-        <v>90</v>
-      </c>
-      <c r="E36" s="9">
-        <v>90</v>
-      </c>
-      <c r="F36" s="9">
-        <v>300</v>
-      </c>
-      <c r="G36" s="9">
-        <v>6</v>
-      </c>
-      <c r="H36" s="9">
-        <v>180</v>
-      </c>
-      <c r="I36" s="10">
-        <f t="shared" si="2"/>
-        <v>1080</v>
-      </c>
-      <c r="J36" s="10">
-        <f t="shared" si="3"/>
-        <v>360</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="8">
-        <v>46282</v>
-      </c>
-      <c r="B37" s="9">
-        <v>390</v>
-      </c>
-      <c r="C37" s="9">
-        <v>30</v>
-      </c>
-      <c r="D37" s="9">
-        <v>60</v>
-      </c>
-      <c r="E37" s="9">
-        <v>90</v>
-      </c>
-      <c r="F37" s="9">
-        <v>350</v>
-      </c>
-      <c r="G37" s="9">
-        <v>7</v>
-      </c>
-      <c r="H37" s="9">
-        <v>30</v>
-      </c>
-      <c r="I37" s="10">
-        <f t="shared" si="2"/>
-        <v>950</v>
-      </c>
-      <c r="J37" s="10">
-        <f t="shared" si="3"/>
-        <v>490</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B38" s="9">
-        <v>390</v>
-      </c>
-      <c r="C38" s="9">
-        <v>30</v>
-      </c>
-      <c r="D38" s="9">
-        <v>120</v>
-      </c>
-      <c r="E38" s="9">
-        <v>90</v>
-      </c>
-      <c r="F38" s="9">
-        <v>0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9">
-        <v>60</v>
-      </c>
-      <c r="I38" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
-      </c>
-      <c r="J38" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B39" s="9">
-        <v>390</v>
-      </c>
-      <c r="C39" s="9">
-        <v>30</v>
-      </c>
-      <c r="D39" s="9">
-        <v>90</v>
-      </c>
-      <c r="E39" s="9">
-        <v>90</v>
-      </c>
-      <c r="F39" s="9">
-        <v>0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9">
-        <v>90</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
-      </c>
-      <c r="J39" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M39" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B40" s="9">
-        <v>390</v>
-      </c>
-      <c r="C40" s="9">
-        <v>30</v>
-      </c>
-      <c r="D40" s="9">
-        <v>90</v>
-      </c>
-      <c r="E40" s="9">
-        <v>60</v>
-      </c>
-      <c r="F40" s="9">
-        <v>0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>0</v>
-      </c>
-      <c r="H40" s="9">
-        <v>90</v>
-      </c>
-      <c r="I40" s="10">
-        <f t="shared" si="2"/>
-        <v>660</v>
-      </c>
-      <c r="J40" s="10">
-        <f t="shared" si="3"/>
-        <v>780</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M40" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N40" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B41" s="9">
-        <v>390</v>
-      </c>
-      <c r="C41" s="9">
-        <v>30</v>
-      </c>
-      <c r="D41" s="9">
-        <v>60</v>
-      </c>
-      <c r="E41" s="9">
-        <v>60</v>
-      </c>
-      <c r="F41" s="9">
-        <v>0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>90</v>
-      </c>
-      <c r="I41" s="10">
-        <f t="shared" si="2"/>
-        <v>630</v>
-      </c>
-      <c r="J41" s="10">
-        <f t="shared" si="3"/>
-        <v>810</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M41" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N41" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="8">
-        <v>46287</v>
-      </c>
-      <c r="B42" s="9">
-        <v>390</v>
-      </c>
-      <c r="C42" s="9">
-        <v>30</v>
-      </c>
-      <c r="D42" s="9">
-        <v>60</v>
-      </c>
-      <c r="E42" s="9">
-        <v>90</v>
-      </c>
-      <c r="F42" s="9">
-        <v>300</v>
-      </c>
-      <c r="G42" s="9">
-        <v>5</v>
-      </c>
-      <c r="H42" s="9">
-        <v>30</v>
-      </c>
-      <c r="I42" s="10">
-        <f t="shared" ref="I42:I44" si="4">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
-        <v>900</v>
-      </c>
-      <c r="J42" s="10">
-        <f t="shared" ref="J42:J44" si="5">IF(I42="","",1440-I42)</f>
-        <v>540</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L42" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M42" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N42" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="8">
-        <v>46288</v>
-      </c>
-      <c r="B43" s="9">
-        <v>390</v>
-      </c>
-      <c r="C43" s="9">
-        <v>30</v>
-      </c>
-      <c r="D43" s="9">
-        <v>90</v>
-      </c>
-      <c r="E43" s="9">
-        <v>90</v>
-      </c>
-      <c r="F43" s="9">
-        <v>300</v>
-      </c>
-      <c r="G43" s="9">
-        <v>6</v>
-      </c>
-      <c r="H43" s="9">
-        <v>180</v>
-      </c>
-      <c r="I43" s="10">
-        <f t="shared" si="4"/>
-        <v>1080</v>
-      </c>
-      <c r="J43" s="10">
-        <f t="shared" si="5"/>
-        <v>360</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N43" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="8">
-        <v>46289</v>
-      </c>
-      <c r="B44" s="9">
-        <v>390</v>
-      </c>
-      <c r="C44" s="9">
-        <v>30</v>
-      </c>
-      <c r="D44" s="9">
-        <v>60</v>
-      </c>
-      <c r="E44" s="9">
-        <v>90</v>
-      </c>
-      <c r="F44" s="9">
-        <v>350</v>
-      </c>
-      <c r="G44" s="9">
-        <v>7</v>
-      </c>
-      <c r="H44" s="9">
-        <v>30</v>
-      </c>
-      <c r="I44" s="10">
-        <f t="shared" si="4"/>
-        <v>950</v>
-      </c>
-      <c r="J44" s="10">
-        <f t="shared" si="5"/>
-        <v>490</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
-    </row>
-    <row r="66" spans="1:14">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
-    </row>
-    <row r="67" spans="1:14">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
-    </row>
-    <row r="68" spans="1:14">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
-    </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
-    </row>
-    <row r="77" spans="1:14">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
-    </row>
-    <row r="79" spans="1:14">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
-    </row>
-    <row r="80" spans="1:14">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
-    </row>
-    <row r="81" spans="1:14">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="12"/>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="12"/>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J84" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="12"/>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J85" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="12"/>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J86" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="12"/>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J87" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="12"/>
-    </row>
-    <row r="88" spans="1:14">
-      <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J88" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="11"/>
-      <c r="N88" s="12"/>
-    </row>
-    <row r="89" spans="1:14">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J89" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-      <c r="M89" s="11"/>
-      <c r="N89" s="12"/>
-    </row>
-    <row r="90" spans="1:14">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J90" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
-      <c r="M90" s="11"/>
-      <c r="N90" s="12"/>
-    </row>
-    <row r="91" spans="1:14">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J91" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
-      <c r="M91" s="11"/>
-      <c r="N91" s="12"/>
-    </row>
-    <row r="92" spans="1:14">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J92" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K92" s="11"/>
-      <c r="L92" s="11"/>
-      <c r="M92" s="11"/>
-      <c r="N92" s="12"/>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J93" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="12"/>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" s="8"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J94" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K94" s="11"/>
-      <c r="L94" s="11"/>
-      <c r="M94" s="11"/>
-      <c r="N94" s="12"/>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" s="8"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J95" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
-      <c r="M95" s="11"/>
-      <c r="N95" s="12"/>
-    </row>
-    <row r="96" spans="1:14">
-      <c r="A96" s="8"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J96" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K96" s="11"/>
-      <c r="L96" s="11"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="12"/>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="A97" s="8"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J97" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K97" s="11"/>
-      <c r="L97" s="11"/>
-      <c r="M97" s="11"/>
-      <c r="N97" s="12"/>
-    </row>
-    <row r="98" spans="1:14">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J98" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K98" s="11"/>
-      <c r="L98" s="11"/>
-      <c r="M98" s="11"/>
-      <c r="N98" s="12"/>
-    </row>
-    <row r="99" spans="1:14">
-      <c r="A99" s="8"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J99" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K99" s="11"/>
-      <c r="L99" s="11"/>
-      <c r="M99" s="11"/>
-      <c r="N99" s="12"/>
-    </row>
-    <row r="100" spans="1:14">
-      <c r="A100" s="8"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J100" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K100" s="11"/>
-      <c r="L100" s="11"/>
-      <c r="M100" s="11"/>
-      <c r="N100" s="12"/>
-    </row>
-    <row r="101" spans="1:14">
-      <c r="A101" s="8"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J101" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K101" s="11"/>
-      <c r="L101" s="11"/>
-      <c r="M101" s="11"/>
-      <c r="N101" s="12"/>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" s="8"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J102" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K102" s="11"/>
-      <c r="L102" s="11"/>
-      <c r="M102" s="11"/>
-      <c r="N102" s="12"/>
-    </row>
-    <row r="103" spans="1:14">
-      <c r="A103" s="8"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J103" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K103" s="11"/>
-      <c r="L103" s="11"/>
-      <c r="M103" s="11"/>
-      <c r="N103" s="12"/>
-    </row>
-    <row r="104" spans="1:14">
-      <c r="A104" s="8"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J104" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K104" s="11"/>
-      <c r="L104" s="11"/>
-      <c r="M104" s="11"/>
-      <c r="N104" s="12"/>
-    </row>
-    <row r="105" spans="1:14">
-      <c r="A105" s="8"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="9"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J105" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K105" s="11"/>
-      <c r="L105" s="11"/>
-      <c r="M105" s="11"/>
-      <c r="N105" s="12"/>
-    </row>
-    <row r="106" spans="1:14">
-      <c r="A106" s="8"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J106" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K106" s="11"/>
-      <c r="L106" s="11"/>
-      <c r="M106" s="11"/>
-      <c r="N106" s="12"/>
-    </row>
-    <row r="107" spans="1:14">
-      <c r="A107" s="8"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J107" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K107" s="11"/>
-      <c r="L107" s="11"/>
-      <c r="M107" s="11"/>
-      <c r="N107" s="12"/>
-    </row>
-    <row r="108" spans="1:14">
-      <c r="A108" s="8"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="9"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="9"/>
-      <c r="I108" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J108" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K108" s="11"/>
-      <c r="L108" s="11"/>
-      <c r="M108" s="11"/>
-      <c r="N108" s="12"/>
-    </row>
-    <row r="109" spans="1:14">
-      <c r="A109" s="8"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J109" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K109" s="11"/>
-      <c r="L109" s="11"/>
-      <c r="M109" s="11"/>
-      <c r="N109" s="12"/>
-    </row>
-    <row r="110" spans="1:14">
-      <c r="A110" s="8"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J110" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K110" s="11"/>
-      <c r="L110" s="11"/>
-      <c r="M110" s="11"/>
-      <c r="N110" s="12"/>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" s="8"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J111" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K111" s="11"/>
-      <c r="L111" s="11"/>
-      <c r="M111" s="11"/>
-      <c r="N111" s="12"/>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" s="8"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J112" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K112" s="11"/>
-      <c r="L112" s="11"/>
-      <c r="M112" s="11"/>
-      <c r="N112" s="12"/>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" s="8"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9"/>
-      <c r="G113" s="9"/>
-      <c r="H113" s="9"/>
-      <c r="I113" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J113" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K113" s="11"/>
-      <c r="L113" s="11"/>
-      <c r="M113" s="11"/>
-      <c r="N113" s="12"/>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" s="8"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J114" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K114" s="11"/>
-      <c r="L114" s="11"/>
-      <c r="M114" s="11"/>
-      <c r="N114" s="12"/>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" s="8"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="9"/>
-      <c r="G115" s="9"/>
-      <c r="H115" s="9"/>
-      <c r="I115" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J115" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K115" s="11"/>
-      <c r="L115" s="11"/>
-      <c r="M115" s="11"/>
-      <c r="N115" s="12"/>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" s="8"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="9"/>
-      <c r="H116" s="9"/>
-      <c r="I116" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J116" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K116" s="11"/>
-      <c r="L116" s="11"/>
-      <c r="M116" s="11"/>
-      <c r="N116" s="12"/>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" s="8"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
-      <c r="I117" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J117" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K117" s="11"/>
-      <c r="L117" s="11"/>
-      <c r="M117" s="11"/>
-      <c r="N117" s="12"/>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" s="8"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J118" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K118" s="11"/>
-      <c r="L118" s="11"/>
-      <c r="M118" s="11"/>
-      <c r="N118" s="12"/>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" s="8"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
-      <c r="I119" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J119" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K119" s="11"/>
-      <c r="L119" s="11"/>
-      <c r="M119" s="11"/>
-      <c r="N119" s="12"/>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" s="8"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J120" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K120" s="11"/>
-      <c r="L120" s="11"/>
-      <c r="M120" s="11"/>
-      <c r="N120" s="12"/>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" s="8"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
-      <c r="I121" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J121" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K121" s="11"/>
-      <c r="L121" s="11"/>
-      <c r="M121" s="11"/>
-      <c r="N121" s="12"/>
-    </row>
-    <row r="122" spans="1:14">
-      <c r="A122" s="8"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J122" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K122" s="11"/>
-      <c r="L122" s="11"/>
-      <c r="M122" s="11"/>
-      <c r="N122" s="12"/>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="A123" s="8"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J123" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K123" s="11"/>
-      <c r="L123" s="11"/>
-      <c r="M123" s="11"/>
-      <c r="N123" s="12"/>
-    </row>
-    <row r="124" spans="1:14">
-      <c r="A124" s="8"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
-      <c r="I124" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J124" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K124" s="11"/>
-      <c r="L124" s="11"/>
-      <c r="M124" s="11"/>
-      <c r="N124" s="12"/>
-    </row>
-    <row r="125" spans="1:14">
-      <c r="A125" s="8"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
-      <c r="I125" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J125" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K125" s="11"/>
-      <c r="L125" s="11"/>
-      <c r="M125" s="11"/>
-      <c r="N125" s="12"/>
-    </row>
-    <row r="126" spans="1:14">
-      <c r="A126" s="8"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
-      <c r="I126" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J126" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K126" s="11"/>
-      <c r="L126" s="11"/>
-      <c r="M126" s="11"/>
-      <c r="N126" s="12"/>
-    </row>
-    <row r="127" spans="1:14">
-      <c r="A127" s="8"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J127" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K127" s="11"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-      <c r="N127" s="12"/>
-    </row>
-    <row r="128" spans="1:14">
-      <c r="A128" s="8"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J128" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K128" s="11"/>
-      <c r="L128" s="11"/>
-      <c r="M128" s="11"/>
-      <c r="N128" s="12"/>
-    </row>
-    <row r="129" spans="1:14">
-      <c r="A129" s="8"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J129" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K129" s="11"/>
-      <c r="L129" s="11"/>
-      <c r="M129" s="11"/>
-      <c r="N129" s="12"/>
-    </row>
-    <row r="130" spans="1:14">
-      <c r="A130" s="8"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J130" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K130" s="11"/>
-      <c r="L130" s="11"/>
-      <c r="M130" s="11"/>
-      <c r="N130" s="12"/>
-    </row>
-    <row r="131" spans="1:14">
-      <c r="A131" s="8"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J131" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K131" s="11"/>
-      <c r="L131" s="11"/>
-      <c r="M131" s="11"/>
-      <c r="N131" s="12"/>
-    </row>
-    <row r="132" spans="1:14">
-      <c r="A132" s="8"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
-      <c r="I132" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J132" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K132" s="11"/>
-      <c r="L132" s="11"/>
-      <c r="M132" s="11"/>
-      <c r="N132" s="12"/>
-    </row>
-    <row r="133" spans="1:14">
-      <c r="A133" s="8"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
-      <c r="I133" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J133" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K133" s="11"/>
-      <c r="L133" s="11"/>
-      <c r="M133" s="11"/>
-      <c r="N133" s="12"/>
-    </row>
-    <row r="134" spans="1:14">
-      <c r="A134" s="8"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
-        <v/>
-      </c>
-      <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
-        <v/>
-      </c>
-      <c r="K134" s="11"/>
-      <c r="L134" s="11"/>
-      <c r="M134" s="11"/>
-      <c r="N134" s="12"/>
-    </row>
-    <row r="135" spans="1:14">
-      <c r="A135" s="8"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J135" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K135" s="11"/>
-      <c r="L135" s="11"/>
-      <c r="M135" s="11"/>
-      <c r="N135" s="12"/>
-    </row>
-    <row r="136" spans="1:14">
-      <c r="A136" s="8"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J136" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K136" s="11"/>
-      <c r="L136" s="11"/>
-      <c r="M136" s="11"/>
-      <c r="N136" s="12"/>
-    </row>
-    <row r="137" spans="1:14">
-      <c r="A137" s="8"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J137" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K137" s="11"/>
-      <c r="L137" s="11"/>
-      <c r="M137" s="11"/>
-      <c r="N137" s="12"/>
-    </row>
-    <row r="138" spans="1:14">
-      <c r="A138" s="8"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J138" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K138" s="11"/>
-      <c r="L138" s="11"/>
-      <c r="M138" s="11"/>
-      <c r="N138" s="12"/>
-    </row>
-    <row r="139" spans="1:14">
-      <c r="A139" s="8"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J139" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K139" s="11"/>
-      <c r="L139" s="11"/>
-      <c r="M139" s="11"/>
-      <c r="N139" s="12"/>
-    </row>
-    <row r="140" spans="1:14">
-      <c r="A140" s="8"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J140" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K140" s="11"/>
-      <c r="L140" s="11"/>
-      <c r="M140" s="11"/>
-      <c r="N140" s="12"/>
-    </row>
-    <row r="141" spans="1:14">
-      <c r="A141" s="8"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J141" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K141" s="11"/>
-      <c r="L141" s="11"/>
-      <c r="M141" s="11"/>
-      <c r="N141" s="12"/>
-    </row>
-    <row r="142" spans="1:14">
-      <c r="A142" s="8"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J142" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K142" s="11"/>
-      <c r="L142" s="11"/>
-      <c r="M142" s="11"/>
-      <c r="N142" s="12"/>
-    </row>
-    <row r="143" spans="1:14">
-      <c r="A143" s="8"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J143" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K143" s="11"/>
-      <c r="L143" s="11"/>
-      <c r="M143" s="11"/>
-      <c r="N143" s="12"/>
-    </row>
-    <row r="144" spans="1:14">
-      <c r="A144" s="8"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J144" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K144" s="11"/>
-      <c r="L144" s="11"/>
-      <c r="M144" s="11"/>
-      <c r="N144" s="12"/>
-    </row>
-    <row r="145" spans="1:14">
-      <c r="A145" s="8"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J145" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K145" s="11"/>
-      <c r="L145" s="11"/>
-      <c r="M145" s="11"/>
-      <c r="N145" s="12"/>
-    </row>
-    <row r="146" spans="1:14">
-      <c r="A146" s="8"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J146" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K146" s="11"/>
-      <c r="L146" s="11"/>
-      <c r="M146" s="11"/>
-      <c r="N146" s="12"/>
-    </row>
-    <row r="147" spans="1:14">
-      <c r="A147" s="8"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J147" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K147" s="11"/>
-      <c r="L147" s="11"/>
-      <c r="M147" s="11"/>
-      <c r="N147" s="12"/>
-    </row>
-    <row r="148" spans="1:14">
-      <c r="A148" s="8"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J148" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K148" s="11"/>
-      <c r="L148" s="11"/>
-      <c r="M148" s="11"/>
-      <c r="N148" s="12"/>
-    </row>
-    <row r="149" spans="1:14">
-      <c r="A149" s="8"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
-      <c r="F149" s="9"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
-      <c r="I149" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J149" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K149" s="11"/>
-      <c r="L149" s="11"/>
-      <c r="M149" s="11"/>
-      <c r="N149" s="12"/>
-    </row>
-    <row r="150" spans="1:14">
-      <c r="A150" s="8"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="9"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
-      <c r="I150" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J150" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K150" s="11"/>
-      <c r="L150" s="11"/>
-      <c r="M150" s="11"/>
-      <c r="N150" s="12"/>
-    </row>
-    <row r="151" spans="1:14">
-      <c r="A151" s="8"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
-      <c r="I151" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J151" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K151" s="11"/>
-      <c r="L151" s="11"/>
-      <c r="M151" s="11"/>
-      <c r="N151" s="12"/>
-    </row>
-    <row r="152" spans="1:14">
-      <c r="A152" s="8"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="9"/>
-      <c r="E152" s="9"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="9"/>
-      <c r="H152" s="9"/>
-      <c r="I152" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J152" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K152" s="11"/>
-      <c r="L152" s="11"/>
-      <c r="M152" s="11"/>
-      <c r="N152" s="12"/>
-    </row>
-    <row r="153" spans="1:14">
-      <c r="A153" s="8"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
-      <c r="I153" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J153" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K153" s="11"/>
-      <c r="L153" s="11"/>
-      <c r="M153" s="11"/>
-      <c r="N153" s="12"/>
-    </row>
-    <row r="154" spans="1:14">
-      <c r="A154" s="8"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="9"/>
-      <c r="H154" s="9"/>
-      <c r="I154" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J154" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K154" s="11"/>
-      <c r="L154" s="11"/>
-      <c r="M154" s="11"/>
-      <c r="N154" s="12"/>
-    </row>
-    <row r="155" spans="1:14">
-      <c r="A155" s="8"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="9"/>
-      <c r="G155" s="9"/>
-      <c r="H155" s="9"/>
-      <c r="I155" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J155" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K155" s="11"/>
-      <c r="L155" s="11"/>
-      <c r="M155" s="11"/>
-      <c r="N155" s="12"/>
-    </row>
-    <row r="156" spans="1:14">
-      <c r="A156" s="8"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9"/>
-      <c r="H156" s="9"/>
-      <c r="I156" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J156" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K156" s="11"/>
-      <c r="L156" s="11"/>
-      <c r="M156" s="11"/>
-      <c r="N156" s="12"/>
-    </row>
-    <row r="157" spans="1:14">
-      <c r="A157" s="8"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
-      <c r="I157" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J157" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K157" s="11"/>
-      <c r="L157" s="11"/>
-      <c r="M157" s="11"/>
-      <c r="N157" s="12"/>
-    </row>
-    <row r="158" spans="1:14">
-      <c r="A158" s="8"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="9"/>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
-      <c r="I158" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J158" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K158" s="11"/>
-      <c r="L158" s="11"/>
-      <c r="M158" s="11"/>
-      <c r="N158" s="12"/>
-    </row>
-    <row r="159" spans="1:14">
-      <c r="A159" s="8"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
-      <c r="F159" s="9"/>
-      <c r="G159" s="9"/>
-      <c r="H159" s="9"/>
-      <c r="I159" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J159" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K159" s="11"/>
-      <c r="L159" s="11"/>
-      <c r="M159" s="11"/>
-      <c r="N159" s="12"/>
-    </row>
-    <row r="160" spans="1:14">
-      <c r="A160" s="8"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
-      <c r="F160" s="9"/>
-      <c r="G160" s="9"/>
-      <c r="H160" s="9"/>
-      <c r="I160" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J160" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K160" s="11"/>
-      <c r="L160" s="11"/>
-      <c r="M160" s="11"/>
-      <c r="N160" s="12"/>
-    </row>
-    <row r="161" spans="1:14">
-      <c r="A161" s="8"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
-      <c r="F161" s="9"/>
-      <c r="G161" s="9"/>
-      <c r="H161" s="9"/>
-      <c r="I161" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J161" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K161" s="11"/>
-      <c r="L161" s="11"/>
-      <c r="M161" s="11"/>
-      <c r="N161" s="12"/>
-    </row>
-    <row r="162" spans="1:14">
-      <c r="A162" s="8"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
-      <c r="I162" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J162" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K162" s="11"/>
-      <c r="L162" s="11"/>
-      <c r="M162" s="11"/>
-      <c r="N162" s="12"/>
-    </row>
-    <row r="163" spans="1:14">
-      <c r="A163" s="8"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="9"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="9"/>
-      <c r="I163" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J163" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K163" s="11"/>
-      <c r="L163" s="11"/>
-      <c r="M163" s="11"/>
-      <c r="N163" s="12"/>
-    </row>
-    <row r="164" spans="1:14">
-      <c r="A164" s="8"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
-      <c r="F164" s="9"/>
-      <c r="G164" s="9"/>
-      <c r="H164" s="9"/>
-      <c r="I164" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J164" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K164" s="11"/>
-      <c r="L164" s="11"/>
-      <c r="M164" s="11"/>
-      <c r="N164" s="12"/>
-    </row>
-    <row r="165" spans="1:14">
-      <c r="A165" s="8"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
-      <c r="F165" s="9"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="9"/>
-      <c r="I165" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J165" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K165" s="11"/>
-      <c r="L165" s="11"/>
-      <c r="M165" s="11"/>
-      <c r="N165" s="12"/>
-    </row>
-    <row r="166" spans="1:14">
-      <c r="A166" s="8"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
-      <c r="F166" s="9"/>
-      <c r="G166" s="9"/>
-      <c r="H166" s="9"/>
-      <c r="I166" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J166" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K166" s="11"/>
-      <c r="L166" s="11"/>
-      <c r="M166" s="11"/>
-      <c r="N166" s="12"/>
-    </row>
-    <row r="167" spans="1:14">
-      <c r="A167" s="8"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
-      <c r="D167" s="9"/>
-      <c r="E167" s="9"/>
-      <c r="F167" s="9"/>
-      <c r="G167" s="9"/>
-      <c r="H167" s="9"/>
-      <c r="I167" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J167" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K167" s="11"/>
-      <c r="L167" s="11"/>
-      <c r="M167" s="11"/>
-      <c r="N167" s="12"/>
-    </row>
-    <row r="168" spans="1:14">
-      <c r="A168" s="8"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="F168" s="9"/>
-      <c r="G168" s="9"/>
-      <c r="H168" s="9"/>
-      <c r="I168" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J168" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K168" s="11"/>
-      <c r="L168" s="11"/>
-      <c r="M168" s="11"/>
-      <c r="N168" s="12"/>
-    </row>
-    <row r="169" spans="1:14">
-      <c r="A169" s="8"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="9"/>
-      <c r="I169" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J169" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K169" s="11"/>
-      <c r="L169" s="11"/>
-      <c r="M169" s="11"/>
-      <c r="N169" s="12"/>
-    </row>
-    <row r="170" spans="1:14">
-      <c r="A170" s="8"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
-      <c r="D170" s="9"/>
-      <c r="E170" s="9"/>
-      <c r="F170" s="9"/>
-      <c r="G170" s="9"/>
-      <c r="H170" s="9"/>
-      <c r="I170" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J170" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K170" s="11"/>
-      <c r="L170" s="11"/>
-      <c r="M170" s="11"/>
-      <c r="N170" s="12"/>
-    </row>
-    <row r="171" spans="1:14">
-      <c r="A171" s="8"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
-      <c r="D171" s="9"/>
-      <c r="E171" s="9"/>
-      <c r="F171" s="9"/>
-      <c r="G171" s="9"/>
-      <c r="H171" s="9"/>
-      <c r="I171" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J171" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K171" s="11"/>
-      <c r="L171" s="11"/>
-      <c r="M171" s="11"/>
-      <c r="N171" s="12"/>
-    </row>
-    <row r="172" spans="1:14">
-      <c r="A172" s="8"/>
-      <c r="B172" s="9"/>
-      <c r="C172" s="9"/>
-      <c r="D172" s="9"/>
-      <c r="E172" s="9"/>
-      <c r="F172" s="9"/>
-      <c r="G172" s="9"/>
-      <c r="H172" s="9"/>
-      <c r="I172" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J172" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K172" s="11"/>
-      <c r="L172" s="11"/>
-      <c r="M172" s="11"/>
-      <c r="N172" s="12"/>
-    </row>
-    <row r="173" spans="1:14">
-      <c r="A173" s="8"/>
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9"/>
-      <c r="F173" s="9"/>
-      <c r="G173" s="9"/>
-      <c r="H173" s="9"/>
-      <c r="I173" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J173" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K173" s="11"/>
-      <c r="L173" s="11"/>
-      <c r="M173" s="11"/>
-      <c r="N173" s="12"/>
-    </row>
-    <row r="174" spans="1:14">
-      <c r="A174" s="8"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="9"/>
-      <c r="D174" s="9"/>
-      <c r="E174" s="9"/>
-      <c r="F174" s="9"/>
-      <c r="G174" s="9"/>
-      <c r="H174" s="9"/>
-      <c r="I174" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J174" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K174" s="11"/>
-      <c r="L174" s="11"/>
-      <c r="M174" s="11"/>
-      <c r="N174" s="12"/>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="A175" s="8"/>
-      <c r="B175" s="9"/>
-      <c r="C175" s="9"/>
-      <c r="D175" s="9"/>
-      <c r="E175" s="9"/>
-      <c r="F175" s="9"/>
-      <c r="G175" s="9"/>
-      <c r="H175" s="9"/>
-      <c r="I175" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J175" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K175" s="11"/>
-      <c r="L175" s="11"/>
-      <c r="M175" s="11"/>
-      <c r="N175" s="12"/>
-    </row>
-    <row r="176" spans="1:14">
-      <c r="A176" s="8"/>
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
-      <c r="F176" s="9"/>
-      <c r="G176" s="9"/>
-      <c r="H176" s="9"/>
-      <c r="I176" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J176" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K176" s="11"/>
-      <c r="L176" s="11"/>
-      <c r="M176" s="11"/>
-      <c r="N176" s="12"/>
-    </row>
-    <row r="177" spans="1:14">
-      <c r="A177" s="8"/>
-      <c r="B177" s="9"/>
-      <c r="C177" s="9"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
-      <c r="I177" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J177" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K177" s="11"/>
-      <c r="L177" s="11"/>
-      <c r="M177" s="11"/>
-      <c r="N177" s="12"/>
-    </row>
-    <row r="178" spans="1:14">
-      <c r="A178" s="8"/>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J178" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K178" s="11"/>
-      <c r="L178" s="11"/>
-      <c r="M178" s="11"/>
-      <c r="N178" s="12"/>
-    </row>
-    <row r="179" spans="1:14">
-      <c r="A179" s="8"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
-      <c r="I179" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J179" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K179" s="11"/>
-      <c r="L179" s="11"/>
-      <c r="M179" s="11"/>
-      <c r="N179" s="12"/>
-    </row>
-    <row r="180" spans="1:14">
-      <c r="A180" s="8"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
-      <c r="I180" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J180" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K180" s="11"/>
-      <c r="L180" s="11"/>
-      <c r="M180" s="11"/>
-      <c r="N180" s="12"/>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="A181" s="8"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
-      <c r="I181" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J181" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K181" s="11"/>
-      <c r="L181" s="11"/>
-      <c r="M181" s="11"/>
-      <c r="N181" s="12"/>
-    </row>
-    <row r="182" spans="1:14">
-      <c r="A182" s="8"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
-      <c r="I182" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J182" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K182" s="11"/>
-      <c r="L182" s="11"/>
-      <c r="M182" s="11"/>
-      <c r="N182" s="12"/>
-    </row>
-    <row r="183" spans="1:14">
-      <c r="A183" s="8"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="9"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="9"/>
-      <c r="I183" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J183" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K183" s="11"/>
-      <c r="L183" s="11"/>
-      <c r="M183" s="11"/>
-      <c r="N183" s="12"/>
-    </row>
-    <row r="184" spans="1:14">
-      <c r="A184" s="8"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="9"/>
-      <c r="I184" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J184" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K184" s="11"/>
-      <c r="L184" s="11"/>
-      <c r="M184" s="11"/>
-      <c r="N184" s="12"/>
-    </row>
-    <row r="185" spans="1:14">
-      <c r="A185" s="8"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="9"/>
-      <c r="I185" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J185" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K185" s="11"/>
-      <c r="L185" s="11"/>
-      <c r="M185" s="11"/>
-      <c r="N185" s="12"/>
-    </row>
-    <row r="186" spans="1:14">
-      <c r="A186" s="8"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
-      <c r="I186" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J186" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K186" s="11"/>
-      <c r="L186" s="11"/>
-      <c r="M186" s="11"/>
-      <c r="N186" s="12"/>
-    </row>
-    <row r="187" spans="1:14">
-      <c r="A187" s="8"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="9"/>
-      <c r="I187" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J187" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K187" s="11"/>
-      <c r="L187" s="11"/>
-      <c r="M187" s="11"/>
-      <c r="N187" s="12"/>
-    </row>
-    <row r="188" spans="1:14">
-      <c r="A188" s="8"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
-      <c r="I188" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J188" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K188" s="11"/>
-      <c r="L188" s="11"/>
-      <c r="M188" s="11"/>
-      <c r="N188" s="12"/>
-    </row>
-    <row r="189" spans="1:14">
-      <c r="A189" s="8"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
-      <c r="I189" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J189" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K189" s="11"/>
-      <c r="L189" s="11"/>
-      <c r="M189" s="11"/>
-      <c r="N189" s="12"/>
-    </row>
-    <row r="190" spans="1:14">
-      <c r="A190" s="8"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
-      <c r="I190" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J190" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K190" s="11"/>
-      <c r="L190" s="11"/>
-      <c r="M190" s="11"/>
-      <c r="N190" s="12"/>
-    </row>
-    <row r="191" spans="1:14">
-      <c r="A191" s="8"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
-      <c r="E191" s="9"/>
-      <c r="F191" s="9"/>
-      <c r="G191" s="9"/>
-      <c r="H191" s="9"/>
-      <c r="I191" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J191" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K191" s="11"/>
-      <c r="L191" s="11"/>
-      <c r="M191" s="11"/>
-      <c r="N191" s="12"/>
-    </row>
-    <row r="192" spans="1:14">
-      <c r="A192" s="8"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
-      <c r="E192" s="9"/>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
-      <c r="I192" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J192" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K192" s="11"/>
-      <c r="L192" s="11"/>
-      <c r="M192" s="11"/>
-      <c r="N192" s="12"/>
-    </row>
-    <row r="193" spans="1:14">
-      <c r="A193" s="8"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
-      <c r="F193" s="9"/>
-      <c r="G193" s="9"/>
-      <c r="H193" s="9"/>
-      <c r="I193" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J193" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K193" s="11"/>
-      <c r="L193" s="11"/>
-      <c r="M193" s="11"/>
-      <c r="N193" s="12"/>
-    </row>
-    <row r="194" spans="1:14">
-      <c r="A194" s="8"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="9"/>
-      <c r="E194" s="9"/>
-      <c r="F194" s="9"/>
-      <c r="G194" s="9"/>
-      <c r="H194" s="9"/>
-      <c r="I194" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J194" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K194" s="11"/>
-      <c r="L194" s="11"/>
-      <c r="M194" s="11"/>
-      <c r="N194" s="12"/>
-    </row>
-    <row r="195" spans="1:14">
-      <c r="A195" s="8"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="9"/>
-      <c r="G195" s="9"/>
-      <c r="H195" s="9"/>
-      <c r="I195" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J195" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K195" s="11"/>
-      <c r="L195" s="11"/>
-      <c r="M195" s="11"/>
-      <c r="N195" s="12"/>
-    </row>
-    <row r="196" spans="1:14">
-      <c r="A196" s="8"/>
-      <c r="B196" s="9"/>
-      <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
-      <c r="H196" s="9"/>
-      <c r="I196" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J196" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K196" s="11"/>
-      <c r="L196" s="11"/>
-      <c r="M196" s="11"/>
-      <c r="N196" s="12"/>
-    </row>
-    <row r="197" spans="1:14">
-      <c r="A197" s="8"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9"/>
-      <c r="G197" s="9"/>
-      <c r="H197" s="9"/>
-      <c r="I197" s="10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J197" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K197" s="11"/>
-      <c r="L197" s="11"/>
-      <c r="M197" s="11"/>
-      <c r="N197" s="12"/>
-    </row>
-    <row r="198" spans="1:14">
-      <c r="A198" s="8"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
-      <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
-        <v/>
-      </c>
-      <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
-        <v/>
-      </c>
-      <c r="K198" s="11"/>
-      <c r="L198" s="11"/>
-      <c r="M198" s="11"/>
-      <c r="N198" s="12"/>
-    </row>
-    <row r="199" spans="1:14">
-      <c r="A199" s="8"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
-      <c r="I199" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J199" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K199" s="11"/>
-      <c r="L199" s="11"/>
-      <c r="M199" s="11"/>
-      <c r="N199" s="12"/>
-    </row>
-    <row r="200" spans="1:14">
-      <c r="A200" s="8"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="9"/>
-      <c r="I200" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J200" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K200" s="11"/>
-      <c r="L200" s="11"/>
-      <c r="M200" s="11"/>
-      <c r="N200" s="12"/>
-    </row>
-    <row r="201" spans="1:14">
-      <c r="A201" s="8"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9"/>
-      <c r="G201" s="9"/>
-      <c r="H201" s="9"/>
-      <c r="I201" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J201" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K201" s="11"/>
-      <c r="L201" s="11"/>
-      <c r="M201" s="11"/>
-      <c r="N201" s="12"/>
-    </row>
-    <row r="202" spans="1:14">
-      <c r="A202" s="8"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
-      <c r="D202" s="9"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="9"/>
-      <c r="G202" s="9"/>
-      <c r="H202" s="9"/>
-      <c r="I202" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J202" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K202" s="11"/>
-      <c r="L202" s="11"/>
-      <c r="M202" s="11"/>
-      <c r="N202" s="12"/>
-    </row>
-    <row r="203" spans="1:14">
-      <c r="A203" s="8"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="9"/>
-      <c r="I203" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J203" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K203" s="11"/>
-      <c r="L203" s="11"/>
-      <c r="M203" s="11"/>
-      <c r="N203" s="12"/>
-    </row>
-    <row r="204" spans="1:14">
-      <c r="A204" s="8"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="9"/>
-      <c r="H204" s="9"/>
-      <c r="I204" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J204" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K204" s="11"/>
-      <c r="L204" s="11"/>
-      <c r="M204" s="11"/>
-      <c r="N204" s="12"/>
-    </row>
-    <row r="205" spans="1:14">
-      <c r="A205" s="8"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9"/>
-      <c r="G205" s="9"/>
-      <c r="H205" s="9"/>
-      <c r="I205" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J205" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K205" s="11"/>
-      <c r="L205" s="11"/>
-      <c r="M205" s="11"/>
-      <c r="N205" s="12"/>
-    </row>
-    <row r="206" spans="1:14">
-      <c r="A206" s="8"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
-      <c r="D206" s="9"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9"/>
-      <c r="G206" s="9"/>
-      <c r="H206" s="9"/>
-      <c r="I206" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J206" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K206" s="11"/>
-      <c r="L206" s="11"/>
-      <c r="M206" s="11"/>
-      <c r="N206" s="12"/>
-    </row>
-    <row r="207" spans="1:14">
-      <c r="A207" s="8"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="9"/>
-      <c r="I207" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J207" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K207" s="11"/>
-      <c r="L207" s="11"/>
-      <c r="M207" s="11"/>
-      <c r="N207" s="12"/>
-    </row>
-    <row r="208" spans="1:14">
-      <c r="A208" s="8"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="9"/>
-      <c r="H208" s="9"/>
-      <c r="I208" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J208" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K208" s="11"/>
-      <c r="L208" s="11"/>
-      <c r="M208" s="11"/>
-      <c r="N208" s="12"/>
-    </row>
-    <row r="209" spans="1:14">
-      <c r="A209" s="8"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9"/>
-      <c r="G209" s="9"/>
-      <c r="H209" s="9"/>
-      <c r="I209" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J209" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K209" s="11"/>
-      <c r="L209" s="11"/>
-      <c r="M209" s="11"/>
-      <c r="N209" s="12"/>
-    </row>
-    <row r="210" spans="1:14">
-      <c r="A210" s="8"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9"/>
-      <c r="G210" s="9"/>
-      <c r="H210" s="9"/>
-      <c r="I210" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J210" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K210" s="11"/>
-      <c r="L210" s="11"/>
-      <c r="M210" s="11"/>
-      <c r="N210" s="12"/>
-    </row>
-    <row r="211" spans="1:14">
-      <c r="A211" s="8"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="9"/>
-      <c r="G211" s="9"/>
-      <c r="H211" s="9"/>
-      <c r="I211" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J211" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K211" s="11"/>
-      <c r="L211" s="11"/>
-      <c r="M211" s="11"/>
-      <c r="N211" s="12"/>
-    </row>
-    <row r="212" spans="1:14">
-      <c r="A212" s="8"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
-      <c r="D212" s="9"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="9"/>
-      <c r="G212" s="9"/>
-      <c r="H212" s="9"/>
-      <c r="I212" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J212" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K212" s="11"/>
-      <c r="L212" s="11"/>
-      <c r="M212" s="11"/>
-      <c r="N212" s="12"/>
-    </row>
-    <row r="213" spans="1:14">
-      <c r="A213" s="8"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="9"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="9"/>
-      <c r="G213" s="9"/>
-      <c r="H213" s="9"/>
-      <c r="I213" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J213" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K213" s="11"/>
-      <c r="L213" s="11"/>
-      <c r="M213" s="11"/>
-      <c r="N213" s="12"/>
-    </row>
-    <row r="214" spans="1:14">
-      <c r="A214" s="8"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="9"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="9"/>
-      <c r="G214" s="9"/>
-      <c r="H214" s="9"/>
-      <c r="I214" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J214" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K214" s="11"/>
-      <c r="L214" s="11"/>
-      <c r="M214" s="11"/>
-      <c r="N214" s="12"/>
-    </row>
-    <row r="215" spans="1:14">
-      <c r="A215" s="8"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="9"/>
-      <c r="G215" s="9"/>
-      <c r="H215" s="9"/>
-      <c r="I215" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J215" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K215" s="11"/>
-      <c r="L215" s="11"/>
-      <c r="M215" s="11"/>
-      <c r="N215" s="12"/>
-    </row>
-    <row r="216" spans="1:14">
-      <c r="A216" s="8"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
-      <c r="D216" s="9"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="9"/>
-      <c r="G216" s="9"/>
-      <c r="H216" s="9"/>
-      <c r="I216" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J216" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K216" s="11"/>
-      <c r="L216" s="11"/>
-      <c r="M216" s="11"/>
-      <c r="N216" s="12"/>
-    </row>
-    <row r="217" spans="1:14">
-      <c r="A217" s="8"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9"/>
-      <c r="G217" s="9"/>
-      <c r="H217" s="9"/>
-      <c r="I217" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J217" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K217" s="11"/>
-      <c r="L217" s="11"/>
-      <c r="M217" s="11"/>
-      <c r="N217" s="12"/>
-    </row>
-    <row r="218" spans="1:14">
-      <c r="A218" s="8"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="9"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="9"/>
-      <c r="I218" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J218" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K218" s="11"/>
-      <c r="L218" s="11"/>
-      <c r="M218" s="11"/>
-      <c r="N218" s="12"/>
-    </row>
-    <row r="219" spans="1:14">
-      <c r="A219" s="8"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="9"/>
-      <c r="G219" s="9"/>
-      <c r="H219" s="9"/>
-      <c r="I219" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J219" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K219" s="11"/>
-      <c r="L219" s="11"/>
-      <c r="M219" s="11"/>
-      <c r="N219" s="12"/>
-    </row>
-    <row r="220" spans="1:14">
-      <c r="A220" s="8"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="9"/>
-      <c r="G220" s="9"/>
-      <c r="H220" s="9"/>
-      <c r="I220" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J220" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K220" s="11"/>
-      <c r="L220" s="11"/>
-      <c r="M220" s="11"/>
-      <c r="N220" s="12"/>
-    </row>
-    <row r="221" spans="1:14">
-      <c r="A221" s="8"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="9"/>
-      <c r="G221" s="9"/>
-      <c r="H221" s="9"/>
-      <c r="I221" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J221" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K221" s="11"/>
-      <c r="L221" s="11"/>
-      <c r="M221" s="11"/>
-      <c r="N221" s="12"/>
-    </row>
-    <row r="222" spans="1:14">
-      <c r="A222" s="8"/>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-      <c r="I222" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J222" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K222" s="11"/>
-      <c r="L222" s="11"/>
-      <c r="M222" s="11"/>
-      <c r="N222" s="12"/>
-    </row>
-    <row r="223" spans="1:14">
-      <c r="A223" s="8"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="9"/>
-      <c r="G223" s="9"/>
-      <c r="H223" s="9"/>
-      <c r="I223" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J223" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K223" s="11"/>
-      <c r="L223" s="11"/>
-      <c r="M223" s="11"/>
-      <c r="N223" s="12"/>
-    </row>
-    <row r="224" spans="1:14">
-      <c r="A224" s="8"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="9"/>
-      <c r="G224" s="9"/>
-      <c r="H224" s="9"/>
-      <c r="I224" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J224" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K224" s="11"/>
-      <c r="L224" s="11"/>
-      <c r="M224" s="11"/>
-      <c r="N224" s="12"/>
-    </row>
-    <row r="225" spans="1:14">
-      <c r="A225" s="8"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="9"/>
-      <c r="G225" s="9"/>
-      <c r="H225" s="9"/>
-      <c r="I225" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J225" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K225" s="11"/>
-      <c r="L225" s="11"/>
-      <c r="M225" s="11"/>
-      <c r="N225" s="12"/>
-    </row>
-    <row r="226" spans="1:14">
-      <c r="A226" s="8"/>
-      <c r="B226" s="9"/>
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="9"/>
-      <c r="H226" s="9"/>
-      <c r="I226" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J226" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K226" s="11"/>
-      <c r="L226" s="11"/>
-      <c r="M226" s="11"/>
-      <c r="N226" s="12"/>
-    </row>
-    <row r="227" spans="1:14">
-      <c r="A227" s="8"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
-      <c r="E227" s="9"/>
-      <c r="F227" s="9"/>
-      <c r="G227" s="9"/>
-      <c r="H227" s="9"/>
-      <c r="I227" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J227" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K227" s="11"/>
-      <c r="L227" s="11"/>
-      <c r="M227" s="11"/>
-      <c r="N227" s="12"/>
-    </row>
-    <row r="228" spans="1:14">
-      <c r="A228" s="8"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="F228" s="9"/>
-      <c r="G228" s="9"/>
-      <c r="H228" s="9"/>
-      <c r="I228" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J228" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K228" s="11"/>
-      <c r="L228" s="11"/>
-      <c r="M228" s="11"/>
-      <c r="N228" s="12"/>
-    </row>
-    <row r="229" spans="1:14">
-      <c r="A229" s="8"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="9"/>
-      <c r="G229" s="9"/>
-      <c r="H229" s="9"/>
-      <c r="I229" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J229" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K229" s="11"/>
-      <c r="L229" s="11"/>
-      <c r="M229" s="11"/>
-      <c r="N229" s="12"/>
-    </row>
-    <row r="230" spans="1:14">
-      <c r="A230" s="8"/>
-      <c r="B230" s="9"/>
-      <c r="C230" s="9"/>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="F230" s="9"/>
-      <c r="G230" s="9"/>
-      <c r="H230" s="9"/>
-      <c r="I230" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J230" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K230" s="11"/>
-      <c r="L230" s="11"/>
-      <c r="M230" s="11"/>
-      <c r="N230" s="12"/>
-    </row>
-    <row r="231" spans="1:14">
-      <c r="A231" s="8"/>
-      <c r="B231" s="9"/>
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="F231" s="9"/>
-      <c r="G231" s="9"/>
-      <c r="H231" s="9"/>
-      <c r="I231" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J231" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K231" s="11"/>
-      <c r="L231" s="11"/>
-      <c r="M231" s="11"/>
-      <c r="N231" s="12"/>
-    </row>
-    <row r="232" spans="1:14">
-      <c r="A232" s="8"/>
-      <c r="B232" s="9"/>
-      <c r="C232" s="9"/>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="F232" s="9"/>
-      <c r="G232" s="9"/>
-      <c r="H232" s="9"/>
-      <c r="I232" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J232" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K232" s="11"/>
-      <c r="L232" s="11"/>
-      <c r="M232" s="11"/>
-      <c r="N232" s="12"/>
-    </row>
-    <row r="233" spans="1:14">
-      <c r="A233" s="8"/>
-      <c r="B233" s="9"/>
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="F233" s="9"/>
-      <c r="G233" s="9"/>
-      <c r="H233" s="9"/>
-      <c r="I233" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J233" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K233" s="11"/>
-      <c r="L233" s="11"/>
-      <c r="M233" s="11"/>
-      <c r="N233" s="12"/>
-    </row>
-    <row r="234" spans="1:14">
-      <c r="A234" s="8"/>
-      <c r="B234" s="9"/>
-      <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="F234" s="9"/>
-      <c r="G234" s="9"/>
-      <c r="H234" s="9"/>
-      <c r="I234" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J234" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K234" s="11"/>
-      <c r="L234" s="11"/>
-      <c r="M234" s="11"/>
-      <c r="N234" s="12"/>
-    </row>
-    <row r="235" spans="1:14">
-      <c r="A235" s="8"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="9"/>
-      <c r="G235" s="9"/>
-      <c r="H235" s="9"/>
-      <c r="I235" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J235" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K235" s="11"/>
-      <c r="L235" s="11"/>
-      <c r="M235" s="11"/>
-      <c r="N235" s="12"/>
-    </row>
-    <row r="236" spans="1:14">
-      <c r="A236" s="8"/>
-      <c r="B236" s="9"/>
-      <c r="C236" s="9"/>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="9"/>
-      <c r="G236" s="9"/>
-      <c r="H236" s="9"/>
-      <c r="I236" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J236" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K236" s="11"/>
-      <c r="L236" s="11"/>
-      <c r="M236" s="11"/>
-      <c r="N236" s="12"/>
-    </row>
-    <row r="237" spans="1:14">
-      <c r="A237" s="8"/>
-      <c r="B237" s="9"/>
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="9"/>
-      <c r="G237" s="9"/>
-      <c r="H237" s="9"/>
-      <c r="I237" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J237" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K237" s="11"/>
-      <c r="L237" s="11"/>
-      <c r="M237" s="11"/>
-      <c r="N237" s="12"/>
-    </row>
-    <row r="238" spans="1:14">
-      <c r="A238" s="8"/>
-      <c r="B238" s="9"/>
-      <c r="C238" s="9"/>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="F238" s="9"/>
-      <c r="G238" s="9"/>
-      <c r="H238" s="9"/>
-      <c r="I238" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J238" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K238" s="11"/>
-      <c r="L238" s="11"/>
-      <c r="M238" s="11"/>
-      <c r="N238" s="12"/>
-    </row>
-    <row r="239" spans="1:14">
-      <c r="A239" s="8"/>
-      <c r="B239" s="9"/>
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="F239" s="9"/>
-      <c r="G239" s="9"/>
-      <c r="H239" s="9"/>
-      <c r="I239" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J239" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K239" s="11"/>
-      <c r="L239" s="11"/>
-      <c r="M239" s="11"/>
-      <c r="N239" s="12"/>
-    </row>
-    <row r="240" spans="1:14">
-      <c r="A240" s="8"/>
-      <c r="B240" s="9"/>
-      <c r="C240" s="9"/>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="F240" s="9"/>
-      <c r="G240" s="9"/>
-      <c r="H240" s="9"/>
-      <c r="I240" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J240" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K240" s="11"/>
-      <c r="L240" s="11"/>
-      <c r="M240" s="11"/>
-      <c r="N240" s="12"/>
-    </row>
-    <row r="241" spans="1:14">
-      <c r="A241" s="8"/>
-      <c r="B241" s="9"/>
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
-      <c r="E241" s="9"/>
-      <c r="F241" s="9"/>
-      <c r="G241" s="9"/>
-      <c r="H241" s="9"/>
-      <c r="I241" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J241" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K241" s="11"/>
-      <c r="L241" s="11"/>
-      <c r="M241" s="11"/>
-      <c r="N241" s="12"/>
-    </row>
-    <row r="242" spans="1:14">
-      <c r="A242" s="8"/>
-      <c r="B242" s="9"/>
-      <c r="C242" s="9"/>
-      <c r="D242" s="9"/>
-      <c r="E242" s="9"/>
-      <c r="F242" s="9"/>
-      <c r="G242" s="9"/>
-      <c r="H242" s="9"/>
-      <c r="I242" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J242" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K242" s="11"/>
-      <c r="L242" s="11"/>
-      <c r="M242" s="11"/>
-      <c r="N242" s="12"/>
-    </row>
-    <row r="243" spans="1:14">
-      <c r="A243" s="8"/>
-      <c r="B243" s="9"/>
-      <c r="C243" s="9"/>
-      <c r="D243" s="9"/>
-      <c r="E243" s="9"/>
-      <c r="F243" s="9"/>
-      <c r="G243" s="9"/>
-      <c r="H243" s="9"/>
-      <c r="I243" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J243" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K243" s="11"/>
-      <c r="L243" s="11"/>
-      <c r="M243" s="11"/>
-      <c r="N243" s="12"/>
-    </row>
-    <row r="244" spans="1:14">
-      <c r="A244" s="8"/>
-      <c r="B244" s="9"/>
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
-      <c r="F244" s="9"/>
-      <c r="G244" s="9"/>
-      <c r="H244" s="9"/>
-      <c r="I244" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J244" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K244" s="11"/>
-      <c r="L244" s="11"/>
-      <c r="M244" s="11"/>
-      <c r="N244" s="12"/>
-    </row>
-    <row r="245" spans="1:14">
-      <c r="A245" s="8"/>
-      <c r="B245" s="9"/>
-      <c r="C245" s="9"/>
-      <c r="D245" s="9"/>
-      <c r="E245" s="9"/>
-      <c r="F245" s="9"/>
-      <c r="G245" s="9"/>
-      <c r="H245" s="9"/>
-      <c r="I245" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J245" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K245" s="11"/>
-      <c r="L245" s="11"/>
-      <c r="M245" s="11"/>
-      <c r="N245" s="12"/>
-    </row>
-    <row r="246" spans="1:14">
-      <c r="A246" s="8"/>
-      <c r="B246" s="9"/>
-      <c r="C246" s="9"/>
-      <c r="D246" s="9"/>
-      <c r="E246" s="9"/>
-      <c r="F246" s="9"/>
-      <c r="G246" s="9"/>
-      <c r="H246" s="9"/>
-      <c r="I246" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J246" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K246" s="11"/>
-      <c r="L246" s="11"/>
-      <c r="M246" s="11"/>
-      <c r="N246" s="12"/>
-    </row>
-    <row r="247" spans="1:14">
-      <c r="A247" s="8"/>
-      <c r="B247" s="9"/>
-      <c r="C247" s="9"/>
-      <c r="D247" s="9"/>
-      <c r="E247" s="9"/>
-      <c r="F247" s="9"/>
-      <c r="G247" s="9"/>
-      <c r="H247" s="9"/>
-      <c r="I247" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J247" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K247" s="11"/>
-      <c r="L247" s="11"/>
-      <c r="M247" s="11"/>
-      <c r="N247" s="12"/>
-    </row>
-    <row r="248" spans="1:14">
-      <c r="A248" s="8"/>
-      <c r="B248" s="9"/>
-      <c r="C248" s="9"/>
-      <c r="D248" s="9"/>
-      <c r="E248" s="9"/>
-      <c r="F248" s="9"/>
-      <c r="G248" s="9"/>
-      <c r="H248" s="9"/>
-      <c r="I248" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J248" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K248" s="11"/>
-      <c r="L248" s="11"/>
-      <c r="M248" s="11"/>
-      <c r="N248" s="12"/>
-    </row>
-    <row r="249" spans="1:14">
-      <c r="A249" s="8"/>
-      <c r="B249" s="9"/>
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
-      <c r="E249" s="9"/>
-      <c r="F249" s="9"/>
-      <c r="G249" s="9"/>
-      <c r="H249" s="9"/>
-      <c r="I249" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J249" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K249" s="11"/>
-      <c r="L249" s="11"/>
-      <c r="M249" s="11"/>
-      <c r="N249" s="12"/>
-    </row>
-    <row r="250" spans="1:14">
-      <c r="A250" s="8"/>
-      <c r="B250" s="9"/>
-      <c r="C250" s="9"/>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9"/>
-      <c r="F250" s="9"/>
-      <c r="G250" s="9"/>
-      <c r="H250" s="9"/>
-      <c r="I250" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J250" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K250" s="11"/>
-      <c r="L250" s="11"/>
-      <c r="M250" s="11"/>
-      <c r="N250" s="12"/>
-    </row>
-    <row r="251" spans="1:14">
-      <c r="A251" s="8"/>
-      <c r="B251" s="9"/>
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
-      <c r="E251" s="9"/>
-      <c r="F251" s="9"/>
-      <c r="G251" s="9"/>
-      <c r="H251" s="9"/>
-      <c r="I251" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J251" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K251" s="11"/>
-      <c r="L251" s="11"/>
-      <c r="M251" s="11"/>
-      <c r="N251" s="12"/>
-    </row>
-    <row r="252" spans="1:14">
-      <c r="A252" s="8"/>
-      <c r="B252" s="9"/>
-      <c r="C252" s="9"/>
-      <c r="D252" s="9"/>
-      <c r="E252" s="9"/>
-      <c r="F252" s="9"/>
-      <c r="G252" s="9"/>
-      <c r="H252" s="9"/>
-      <c r="I252" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J252" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K252" s="11"/>
-      <c r="L252" s="11"/>
-      <c r="M252" s="11"/>
-      <c r="N252" s="12"/>
-    </row>
-    <row r="253" spans="1:14">
-      <c r="A253" s="8"/>
-      <c r="B253" s="9"/>
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
-      <c r="E253" s="9"/>
-      <c r="F253" s="9"/>
-      <c r="G253" s="9"/>
-      <c r="H253" s="9"/>
-      <c r="I253" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J253" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K253" s="11"/>
-      <c r="L253" s="11"/>
-      <c r="M253" s="11"/>
-      <c r="N253" s="12"/>
-    </row>
-    <row r="254" spans="1:14">
-      <c r="A254" s="8"/>
-      <c r="B254" s="9"/>
-      <c r="C254" s="9"/>
-      <c r="D254" s="9"/>
-      <c r="E254" s="9"/>
-      <c r="F254" s="9"/>
-      <c r="G254" s="9"/>
-      <c r="H254" s="9"/>
-      <c r="I254" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J254" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K254" s="11"/>
-      <c r="L254" s="11"/>
-      <c r="M254" s="11"/>
-      <c r="N254" s="12"/>
-    </row>
-    <row r="255" spans="1:14">
-      <c r="A255" s="8"/>
-      <c r="B255" s="9"/>
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
-      <c r="E255" s="9"/>
-      <c r="F255" s="9"/>
-      <c r="G255" s="9"/>
-      <c r="H255" s="9"/>
-      <c r="I255" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J255" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K255" s="11"/>
-      <c r="L255" s="11"/>
-      <c r="M255" s="11"/>
-      <c r="N255" s="12"/>
-    </row>
-    <row r="256" spans="1:14">
-      <c r="A256" s="8"/>
-      <c r="B256" s="9"/>
-      <c r="C256" s="9"/>
-      <c r="D256" s="9"/>
-      <c r="E256" s="9"/>
-      <c r="F256" s="9"/>
-      <c r="G256" s="9"/>
-      <c r="H256" s="9"/>
-      <c r="I256" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J256" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K256" s="11"/>
-      <c r="L256" s="11"/>
-      <c r="M256" s="11"/>
-      <c r="N256" s="12"/>
-    </row>
-    <row r="257" spans="1:14">
-      <c r="A257" s="8"/>
-      <c r="B257" s="9"/>
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="F257" s="9"/>
-      <c r="G257" s="9"/>
-      <c r="H257" s="9"/>
-      <c r="I257" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J257" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K257" s="11"/>
-      <c r="L257" s="11"/>
-      <c r="M257" s="11"/>
-      <c r="N257" s="12"/>
-    </row>
-    <row r="258" spans="1:14">
-      <c r="A258" s="8"/>
-      <c r="B258" s="9"/>
-      <c r="C258" s="9"/>
-      <c r="D258" s="9"/>
-      <c r="E258" s="9"/>
-      <c r="F258" s="9"/>
-      <c r="G258" s="9"/>
-      <c r="H258" s="9"/>
-      <c r="I258" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J258" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K258" s="11"/>
-      <c r="L258" s="11"/>
-      <c r="M258" s="11"/>
-      <c r="N258" s="12"/>
-    </row>
-    <row r="259" spans="1:14">
-      <c r="A259" s="8"/>
-      <c r="B259" s="9"/>
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
-      <c r="E259" s="9"/>
-      <c r="F259" s="9"/>
-      <c r="G259" s="9"/>
-      <c r="H259" s="9"/>
-      <c r="I259" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J259" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K259" s="11"/>
-      <c r="L259" s="11"/>
-      <c r="M259" s="11"/>
-      <c r="N259" s="12"/>
-    </row>
-    <row r="260" spans="1:14">
-      <c r="A260" s="8"/>
-      <c r="B260" s="9"/>
-      <c r="C260" s="9"/>
-      <c r="D260" s="9"/>
-      <c r="E260" s="9"/>
-      <c r="F260" s="9"/>
-      <c r="G260" s="9"/>
-      <c r="H260" s="9"/>
-      <c r="I260" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J260" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K260" s="11"/>
-      <c r="L260" s="11"/>
-      <c r="M260" s="11"/>
-      <c r="N260" s="12"/>
-    </row>
-    <row r="261" spans="1:14">
-      <c r="A261" s="8"/>
-      <c r="B261" s="9"/>
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
-      <c r="E261" s="9"/>
-      <c r="F261" s="9"/>
-      <c r="G261" s="9"/>
-      <c r="H261" s="9"/>
-      <c r="I261" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J261" s="10" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K261" s="11"/>
-      <c r="L261" s="11"/>
-      <c r="M261" s="11"/>
-      <c r="N261" s="12"/>
-    </row>
-    <row r="262" spans="1:14">
-      <c r="A262" s="8"/>
-      <c r="B262" s="9"/>
-      <c r="C262" s="9"/>
-      <c r="D262" s="9"/>
-      <c r="E262" s="9"/>
-      <c r="F262" s="9"/>
-      <c r="G262" s="9"/>
-      <c r="H262" s="9"/>
-      <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
-        <v/>
-      </c>
-      <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
-        <v/>
-      </c>
-      <c r="K262" s="11"/>
-      <c r="L262" s="11"/>
-      <c r="M262" s="11"/>
-      <c r="N262" s="12"/>
-    </row>
-    <row r="263" spans="1:14">
-      <c r="A263" s="8"/>
-      <c r="B263" s="9"/>
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="F263" s="9"/>
-      <c r="G263" s="9"/>
-      <c r="H263" s="9"/>
-      <c r="I263" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J263" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K263" s="11"/>
-      <c r="L263" s="11"/>
-      <c r="M263" s="11"/>
-      <c r="N263" s="12"/>
-    </row>
-    <row r="264" spans="1:14">
-      <c r="A264" s="8"/>
-      <c r="B264" s="9"/>
-      <c r="C264" s="9"/>
-      <c r="D264" s="9"/>
-      <c r="E264" s="9"/>
-      <c r="F264" s="9"/>
-      <c r="G264" s="9"/>
-      <c r="H264" s="9"/>
-      <c r="I264" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J264" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K264" s="11"/>
-      <c r="L264" s="11"/>
-      <c r="M264" s="11"/>
-      <c r="N264" s="12"/>
-    </row>
-    <row r="265" spans="1:14">
-      <c r="A265" s="8"/>
-      <c r="B265" s="9"/>
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
-      <c r="E265" s="9"/>
-      <c r="F265" s="9"/>
-      <c r="G265" s="9"/>
-      <c r="H265" s="9"/>
-      <c r="I265" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J265" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K265" s="11"/>
-      <c r="L265" s="11"/>
-      <c r="M265" s="11"/>
-      <c r="N265" s="12"/>
-    </row>
-    <row r="266" spans="1:14">
-      <c r="A266" s="8"/>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
-      <c r="I266" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J266" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K266" s="11"/>
-      <c r="L266" s="11"/>
-      <c r="M266" s="11"/>
-      <c r="N266" s="12"/>
-    </row>
-    <row r="267" spans="1:14">
-      <c r="A267" s="8"/>
-      <c r="B267" s="9"/>
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
-      <c r="E267" s="9"/>
-      <c r="F267" s="9"/>
-      <c r="G267" s="9"/>
-      <c r="H267" s="9"/>
-      <c r="I267" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J267" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K267" s="11"/>
-      <c r="L267" s="11"/>
-      <c r="M267" s="11"/>
-      <c r="N267" s="12"/>
-    </row>
-    <row r="268" spans="1:14">
-      <c r="A268" s="8"/>
-      <c r="B268" s="9"/>
-      <c r="C268" s="9"/>
-      <c r="D268" s="9"/>
-      <c r="E268" s="9"/>
-      <c r="F268" s="9"/>
-      <c r="G268" s="9"/>
-      <c r="H268" s="9"/>
-      <c r="I268" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J268" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K268" s="11"/>
-      <c r="L268" s="11"/>
-      <c r="M268" s="11"/>
-      <c r="N268" s="12"/>
-    </row>
-    <row r="269" spans="1:14">
-      <c r="A269" s="8"/>
-      <c r="B269" s="9"/>
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="F269" s="9"/>
-      <c r="G269" s="9"/>
-      <c r="H269" s="9"/>
-      <c r="I269" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J269" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K269" s="11"/>
-      <c r="L269" s="11"/>
-      <c r="M269" s="11"/>
-      <c r="N269" s="12"/>
-    </row>
-    <row r="270" spans="1:14">
-      <c r="A270" s="8"/>
-      <c r="B270" s="9"/>
-      <c r="C270" s="9"/>
-      <c r="D270" s="9"/>
-      <c r="E270" s="9"/>
-      <c r="F270" s="9"/>
-      <c r="G270" s="9"/>
-      <c r="H270" s="9"/>
-      <c r="I270" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J270" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K270" s="11"/>
-      <c r="L270" s="11"/>
-      <c r="M270" s="11"/>
-      <c r="N270" s="12"/>
-    </row>
-    <row r="271" spans="1:14">
-      <c r="A271" s="8"/>
-      <c r="B271" s="9"/>
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
-      <c r="E271" s="9"/>
-      <c r="F271" s="9"/>
-      <c r="G271" s="9"/>
-      <c r="H271" s="9"/>
-      <c r="I271" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J271" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K271" s="11"/>
-      <c r="L271" s="11"/>
-      <c r="M271" s="11"/>
-      <c r="N271" s="12"/>
-    </row>
-    <row r="272" spans="1:14">
-      <c r="A272" s="8"/>
-      <c r="B272" s="9"/>
-      <c r="C272" s="9"/>
-      <c r="D272" s="9"/>
-      <c r="E272" s="9"/>
-      <c r="F272" s="9"/>
-      <c r="G272" s="9"/>
-      <c r="H272" s="9"/>
-      <c r="I272" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J272" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K272" s="11"/>
-      <c r="L272" s="11"/>
-      <c r="M272" s="11"/>
-      <c r="N272" s="12"/>
-    </row>
-    <row r="273" spans="1:14">
-      <c r="A273" s="8"/>
-      <c r="B273" s="9"/>
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
-      <c r="E273" s="9"/>
-      <c r="F273" s="9"/>
-      <c r="G273" s="9"/>
-      <c r="H273" s="9"/>
-      <c r="I273" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J273" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K273" s="11"/>
-      <c r="L273" s="11"/>
-      <c r="M273" s="11"/>
-      <c r="N273" s="12"/>
-    </row>
-    <row r="274" spans="1:14">
-      <c r="A274" s="8"/>
-      <c r="B274" s="9"/>
-      <c r="C274" s="9"/>
-      <c r="D274" s="9"/>
-      <c r="E274" s="9"/>
-      <c r="F274" s="9"/>
-      <c r="G274" s="9"/>
-      <c r="H274" s="9"/>
-      <c r="I274" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J274" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K274" s="11"/>
-      <c r="L274" s="11"/>
-      <c r="M274" s="11"/>
-      <c r="N274" s="12"/>
-    </row>
-    <row r="275" spans="1:14">
-      <c r="A275" s="8"/>
-      <c r="B275" s="9"/>
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
-      <c r="E275" s="9"/>
-      <c r="F275" s="9"/>
-      <c r="G275" s="9"/>
-      <c r="H275" s="9"/>
-      <c r="I275" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J275" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K275" s="11"/>
-      <c r="L275" s="11"/>
-      <c r="M275" s="11"/>
-      <c r="N275" s="12"/>
-    </row>
-    <row r="276" spans="1:14">
-      <c r="A276" s="8"/>
-      <c r="B276" s="9"/>
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="F276" s="9"/>
-      <c r="G276" s="9"/>
-      <c r="H276" s="9"/>
-      <c r="I276" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J276" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K276" s="11"/>
-      <c r="L276" s="11"/>
-      <c r="M276" s="11"/>
-      <c r="N276" s="12"/>
-    </row>
-    <row r="277" spans="1:14">
-      <c r="A277" s="8"/>
-      <c r="B277" s="9"/>
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
-      <c r="E277" s="9"/>
-      <c r="F277" s="9"/>
-      <c r="G277" s="9"/>
-      <c r="H277" s="9"/>
-      <c r="I277" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J277" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K277" s="11"/>
-      <c r="L277" s="11"/>
-      <c r="M277" s="11"/>
-      <c r="N277" s="12"/>
-    </row>
-    <row r="278" spans="1:14">
-      <c r="A278" s="8"/>
-      <c r="B278" s="9"/>
-      <c r="C278" s="9"/>
-      <c r="D278" s="9"/>
-      <c r="E278" s="9"/>
-      <c r="F278" s="9"/>
-      <c r="G278" s="9"/>
-      <c r="H278" s="9"/>
-      <c r="I278" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J278" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K278" s="11"/>
-      <c r="L278" s="11"/>
-      <c r="M278" s="11"/>
-      <c r="N278" s="12"/>
-    </row>
-    <row r="279" spans="1:14">
-      <c r="A279" s="8"/>
-      <c r="B279" s="9"/>
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
-      <c r="E279" s="9"/>
-      <c r="F279" s="9"/>
-      <c r="G279" s="9"/>
-      <c r="H279" s="9"/>
-      <c r="I279" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J279" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K279" s="11"/>
-      <c r="L279" s="11"/>
-      <c r="M279" s="11"/>
-      <c r="N279" s="12"/>
-    </row>
-    <row r="280" spans="1:14">
-      <c r="A280" s="8"/>
-      <c r="B280" s="9"/>
-      <c r="C280" s="9"/>
-      <c r="D280" s="9"/>
-      <c r="E280" s="9"/>
-      <c r="F280" s="9"/>
-      <c r="G280" s="9"/>
-      <c r="H280" s="9"/>
-      <c r="I280" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J280" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K280" s="11"/>
-      <c r="L280" s="11"/>
-      <c r="M280" s="11"/>
-      <c r="N280" s="12"/>
-    </row>
-    <row r="281" spans="1:14">
-      <c r="A281" s="8"/>
-      <c r="B281" s="9"/>
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
-      <c r="E281" s="9"/>
-      <c r="F281" s="9"/>
-      <c r="G281" s="9"/>
-      <c r="H281" s="9"/>
-      <c r="I281" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J281" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K281" s="11"/>
-      <c r="L281" s="11"/>
-      <c r="M281" s="11"/>
-      <c r="N281" s="12"/>
-    </row>
-    <row r="282" spans="1:14">
-      <c r="A282" s="8"/>
-      <c r="B282" s="9"/>
-      <c r="C282" s="9"/>
-      <c r="D282" s="9"/>
-      <c r="E282" s="9"/>
-      <c r="F282" s="9"/>
-      <c r="G282" s="9"/>
-      <c r="H282" s="9"/>
-      <c r="I282" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J282" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K282" s="11"/>
-      <c r="L282" s="11"/>
-      <c r="M282" s="11"/>
-      <c r="N282" s="12"/>
-    </row>
-    <row r="283" spans="1:14">
-      <c r="A283" s="8"/>
-      <c r="B283" s="9"/>
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
-      <c r="E283" s="9"/>
-      <c r="F283" s="9"/>
-      <c r="G283" s="9"/>
-      <c r="H283" s="9"/>
-      <c r="I283" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J283" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K283" s="11"/>
-      <c r="L283" s="11"/>
-      <c r="M283" s="11"/>
-      <c r="N283" s="12"/>
-    </row>
-    <row r="284" spans="1:14">
-      <c r="A284" s="8"/>
-      <c r="B284" s="9"/>
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="F284" s="9"/>
-      <c r="G284" s="9"/>
-      <c r="H284" s="9"/>
-      <c r="I284" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J284" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K284" s="11"/>
-      <c r="L284" s="11"/>
-      <c r="M284" s="11"/>
-      <c r="N284" s="12"/>
-    </row>
-    <row r="285" spans="1:14">
-      <c r="A285" s="8"/>
-      <c r="B285" s="9"/>
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
-      <c r="E285" s="9"/>
-      <c r="F285" s="9"/>
-      <c r="G285" s="9"/>
-      <c r="H285" s="9"/>
-      <c r="I285" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J285" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K285" s="11"/>
-      <c r="L285" s="11"/>
-      <c r="M285" s="11"/>
-      <c r="N285" s="12"/>
-    </row>
-    <row r="286" spans="1:14">
-      <c r="A286" s="8"/>
-      <c r="B286" s="9"/>
-      <c r="C286" s="9"/>
-      <c r="D286" s="9"/>
-      <c r="E286" s="9"/>
-      <c r="F286" s="9"/>
-      <c r="G286" s="9"/>
-      <c r="H286" s="9"/>
-      <c r="I286" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J286" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K286" s="11"/>
-      <c r="L286" s="11"/>
-      <c r="M286" s="11"/>
-      <c r="N286" s="12"/>
-    </row>
-    <row r="287" spans="1:14">
-      <c r="A287" s="8"/>
-      <c r="B287" s="9"/>
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
-      <c r="E287" s="9"/>
-      <c r="F287" s="9"/>
-      <c r="G287" s="9"/>
-      <c r="H287" s="9"/>
-      <c r="I287" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J287" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K287" s="11"/>
-      <c r="L287" s="11"/>
-      <c r="M287" s="11"/>
-      <c r="N287" s="12"/>
-    </row>
-    <row r="288" spans="1:14">
-      <c r="A288" s="8"/>
-      <c r="B288" s="9"/>
-      <c r="C288" s="9"/>
-      <c r="D288" s="9"/>
-      <c r="E288" s="9"/>
-      <c r="F288" s="9"/>
-      <c r="G288" s="9"/>
-      <c r="H288" s="9"/>
-      <c r="I288" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J288" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K288" s="11"/>
-      <c r="L288" s="11"/>
-      <c r="M288" s="11"/>
-      <c r="N288" s="12"/>
-    </row>
-    <row r="289" spans="1:14">
-      <c r="A289" s="8"/>
-      <c r="B289" s="9"/>
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
-      <c r="E289" s="9"/>
-      <c r="F289" s="9"/>
-      <c r="G289" s="9"/>
-      <c r="H289" s="9"/>
-      <c r="I289" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J289" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K289" s="11"/>
-      <c r="L289" s="11"/>
-      <c r="M289" s="11"/>
-      <c r="N289" s="12"/>
-    </row>
-    <row r="290" spans="1:14">
-      <c r="A290" s="8"/>
-      <c r="B290" s="9"/>
-      <c r="C290" s="9"/>
-      <c r="D290" s="9"/>
-      <c r="E290" s="9"/>
-      <c r="F290" s="9"/>
-      <c r="G290" s="9"/>
-      <c r="H290" s="9"/>
-      <c r="I290" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J290" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K290" s="11"/>
-      <c r="L290" s="11"/>
-      <c r="M290" s="11"/>
-      <c r="N290" s="12"/>
-    </row>
-    <row r="291" spans="1:14">
-      <c r="A291" s="8"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
-      <c r="E291" s="9"/>
-      <c r="F291" s="9"/>
-      <c r="G291" s="9"/>
-      <c r="H291" s="9"/>
-      <c r="I291" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J291" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K291" s="11"/>
-      <c r="L291" s="11"/>
-      <c r="M291" s="11"/>
-      <c r="N291" s="12"/>
-    </row>
-    <row r="292" spans="1:14">
-      <c r="A292" s="8"/>
-      <c r="B292" s="9"/>
-      <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
-      <c r="E292" s="9"/>
-      <c r="F292" s="9"/>
-      <c r="G292" s="9"/>
-      <c r="H292" s="9"/>
-      <c r="I292" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J292" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K292" s="11"/>
-      <c r="L292" s="11"/>
-      <c r="M292" s="11"/>
-      <c r="N292" s="12"/>
-    </row>
-    <row r="293" spans="1:14">
-      <c r="A293" s="8"/>
-      <c r="B293" s="9"/>
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
-      <c r="E293" s="9"/>
-      <c r="F293" s="9"/>
-      <c r="G293" s="9"/>
-      <c r="H293" s="9"/>
-      <c r="I293" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J293" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K293" s="11"/>
-      <c r="L293" s="11"/>
-      <c r="M293" s="11"/>
-      <c r="N293" s="12"/>
-    </row>
-    <row r="294" spans="1:14">
-      <c r="A294" s="8"/>
-      <c r="B294" s="9"/>
-      <c r="C294" s="9"/>
-      <c r="D294" s="9"/>
-      <c r="E294" s="9"/>
-      <c r="F294" s="9"/>
-      <c r="G294" s="9"/>
-      <c r="H294" s="9"/>
-      <c r="I294" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J294" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K294" s="11"/>
-      <c r="L294" s="11"/>
-      <c r="M294" s="11"/>
-      <c r="N294" s="12"/>
-    </row>
-    <row r="295" spans="1:14">
-      <c r="A295" s="8"/>
-      <c r="B295" s="9"/>
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
-      <c r="E295" s="9"/>
-      <c r="F295" s="9"/>
-      <c r="G295" s="9"/>
-      <c r="H295" s="9"/>
-      <c r="I295" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J295" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K295" s="11"/>
-      <c r="L295" s="11"/>
-      <c r="M295" s="11"/>
-      <c r="N295" s="12"/>
-    </row>
-    <row r="296" spans="1:14">
-      <c r="A296" s="8"/>
-      <c r="B296" s="9"/>
-      <c r="C296" s="9"/>
-      <c r="D296" s="9"/>
-      <c r="E296" s="9"/>
-      <c r="F296" s="9"/>
-      <c r="G296" s="9"/>
-      <c r="H296" s="9"/>
-      <c r="I296" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J296" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K296" s="11"/>
-      <c r="L296" s="11"/>
-      <c r="M296" s="11"/>
-      <c r="N296" s="12"/>
-    </row>
-    <row r="297" spans="1:14">
-      <c r="A297" s="8"/>
-      <c r="B297" s="9"/>
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
-      <c r="E297" s="9"/>
-      <c r="F297" s="9"/>
-      <c r="G297" s="9"/>
-      <c r="H297" s="9"/>
-      <c r="I297" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J297" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K297" s="11"/>
-      <c r="L297" s="11"/>
-      <c r="M297" s="11"/>
-      <c r="N297" s="12"/>
-    </row>
-    <row r="298" spans="1:14">
-      <c r="A298" s="8"/>
-      <c r="B298" s="9"/>
-      <c r="C298" s="9"/>
-      <c r="D298" s="9"/>
-      <c r="E298" s="9"/>
-      <c r="F298" s="9"/>
-      <c r="G298" s="9"/>
-      <c r="H298" s="9"/>
-      <c r="I298" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J298" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K298" s="11"/>
-      <c r="L298" s="11"/>
-      <c r="M298" s="11"/>
-      <c r="N298" s="12"/>
-    </row>
-    <row r="299" spans="1:14">
-      <c r="A299" s="8"/>
-      <c r="B299" s="9"/>
-      <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
-      <c r="E299" s="9"/>
-      <c r="F299" s="9"/>
-      <c r="G299" s="9"/>
-      <c r="H299" s="9"/>
-      <c r="I299" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J299" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K299" s="11"/>
-      <c r="L299" s="11"/>
-      <c r="M299" s="11"/>
-      <c r="N299" s="12"/>
-    </row>
-    <row r="300" spans="1:14">
-      <c r="A300" s="8"/>
-      <c r="B300" s="9"/>
-      <c r="C300" s="9"/>
-      <c r="D300" s="9"/>
-      <c r="E300" s="9"/>
-      <c r="F300" s="9"/>
-      <c r="G300" s="9"/>
-      <c r="H300" s="9"/>
-      <c r="I300" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J300" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K300" s="11"/>
-      <c r="L300" s="11"/>
-      <c r="M300" s="11"/>
-      <c r="N300" s="12"/>
-    </row>
-    <row r="301" spans="1:14">
-      <c r="A301" s="8"/>
-      <c r="B301" s="9"/>
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="F301" s="9"/>
-      <c r="G301" s="9"/>
-      <c r="H301" s="9"/>
-      <c r="I301" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J301" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K301" s="11"/>
-      <c r="L301" s="11"/>
-      <c r="M301" s="11"/>
-      <c r="N301" s="12"/>
-    </row>
-    <row r="302" spans="1:14">
-      <c r="A302" s="8"/>
-      <c r="B302" s="9"/>
-      <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
-      <c r="E302" s="9"/>
-      <c r="F302" s="9"/>
-      <c r="G302" s="9"/>
-      <c r="H302" s="9"/>
-      <c r="I302" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J302" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K302" s="11"/>
-      <c r="L302" s="11"/>
-      <c r="M302" s="11"/>
-      <c r="N302" s="12"/>
-    </row>
-    <row r="303" spans="1:14">
-      <c r="A303" s="8"/>
-      <c r="B303" s="9"/>
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="F303" s="9"/>
-      <c r="G303" s="9"/>
-      <c r="H303" s="9"/>
-      <c r="I303" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J303" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K303" s="11"/>
-      <c r="L303" s="11"/>
-      <c r="M303" s="11"/>
-      <c r="N303" s="12"/>
-    </row>
-    <row r="304" spans="1:14">
-      <c r="A304" s="8"/>
-      <c r="B304" s="9"/>
-      <c r="C304" s="9"/>
-      <c r="D304" s="9"/>
-      <c r="E304" s="9"/>
-      <c r="F304" s="9"/>
-      <c r="G304" s="9"/>
-      <c r="H304" s="9"/>
-      <c r="I304" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J304" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K304" s="11"/>
-      <c r="L304" s="11"/>
-      <c r="M304" s="11"/>
-      <c r="N304" s="12"/>
-    </row>
-    <row r="305" spans="1:14">
-      <c r="A305" s="8"/>
-      <c r="B305" s="9"/>
-      <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="F305" s="9"/>
-      <c r="G305" s="9"/>
-      <c r="H305" s="9"/>
-      <c r="I305" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J305" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K305" s="11"/>
-      <c r="L305" s="11"/>
-      <c r="M305" s="11"/>
-      <c r="N305" s="12"/>
-    </row>
-    <row r="306" spans="1:14">
-      <c r="A306" s="8"/>
-      <c r="B306" s="9"/>
-      <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="F306" s="9"/>
-      <c r="G306" s="9"/>
-      <c r="H306" s="9"/>
-      <c r="I306" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J306" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K306" s="11"/>
-      <c r="L306" s="11"/>
-      <c r="M306" s="11"/>
-      <c r="N306" s="12"/>
-    </row>
-    <row r="307" spans="1:14">
-      <c r="A307" s="8"/>
-      <c r="B307" s="9"/>
-      <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="F307" s="9"/>
-      <c r="G307" s="9"/>
-      <c r="H307" s="9"/>
-      <c r="I307" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J307" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K307" s="11"/>
-      <c r="L307" s="11"/>
-      <c r="M307" s="11"/>
-      <c r="N307" s="12"/>
-    </row>
-    <row r="308" spans="1:14">
-      <c r="A308" s="8"/>
-      <c r="B308" s="9"/>
-      <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="F308" s="9"/>
-      <c r="G308" s="9"/>
-      <c r="H308" s="9"/>
-      <c r="I308" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J308" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K308" s="11"/>
-      <c r="L308" s="11"/>
-      <c r="M308" s="11"/>
-      <c r="N308" s="12"/>
-    </row>
-    <row r="309" spans="1:14">
-      <c r="A309" s="8"/>
-      <c r="B309" s="9"/>
-      <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="F309" s="9"/>
-      <c r="G309" s="9"/>
-      <c r="H309" s="9"/>
-      <c r="I309" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J309" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K309" s="11"/>
-      <c r="L309" s="11"/>
-      <c r="M309" s="11"/>
-      <c r="N309" s="12"/>
-    </row>
-    <row r="310" spans="1:14">
-      <c r="A310" s="8"/>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
-      <c r="I310" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J310" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K310" s="11"/>
-      <c r="L310" s="11"/>
-      <c r="M310" s="11"/>
-      <c r="N310" s="12"/>
-    </row>
-    <row r="311" spans="1:14">
-      <c r="A311" s="8"/>
-      <c r="B311" s="9"/>
-      <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="F311" s="9"/>
-      <c r="G311" s="9"/>
-      <c r="H311" s="9"/>
-      <c r="I311" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J311" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K311" s="11"/>
-      <c r="L311" s="11"/>
-      <c r="M311" s="11"/>
-      <c r="N311" s="12"/>
-    </row>
-    <row r="312" spans="1:14">
-      <c r="A312" s="8"/>
-      <c r="B312" s="9"/>
-      <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="F312" s="9"/>
-      <c r="G312" s="9"/>
-      <c r="H312" s="9"/>
-      <c r="I312" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J312" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K312" s="11"/>
-      <c r="L312" s="11"/>
-      <c r="M312" s="11"/>
-      <c r="N312" s="12"/>
-    </row>
-    <row r="313" spans="1:14">
-      <c r="A313" s="8"/>
-      <c r="B313" s="9"/>
-      <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="F313" s="9"/>
-      <c r="G313" s="9"/>
-      <c r="H313" s="9"/>
-      <c r="I313" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J313" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K313" s="11"/>
-      <c r="L313" s="11"/>
-      <c r="M313" s="11"/>
-      <c r="N313" s="12"/>
-    </row>
-    <row r="314" spans="1:14">
-      <c r="A314" s="8"/>
-      <c r="B314" s="9"/>
-      <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="F314" s="9"/>
-      <c r="G314" s="9"/>
-      <c r="H314" s="9"/>
-      <c r="I314" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J314" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K314" s="11"/>
-      <c r="L314" s="11"/>
-      <c r="M314" s="11"/>
-      <c r="N314" s="12"/>
-    </row>
-    <row r="315" spans="1:14">
-      <c r="A315" s="8"/>
-      <c r="B315" s="9"/>
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="F315" s="9"/>
-      <c r="G315" s="9"/>
-      <c r="H315" s="9"/>
-      <c r="I315" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J315" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K315" s="11"/>
-      <c r="L315" s="11"/>
-      <c r="M315" s="11"/>
-      <c r="N315" s="12"/>
-    </row>
-    <row r="316" spans="1:14">
-      <c r="A316" s="8"/>
-      <c r="B316" s="9"/>
-      <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="F316" s="9"/>
-      <c r="G316" s="9"/>
-      <c r="H316" s="9"/>
-      <c r="I316" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J316" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K316" s="11"/>
-      <c r="L316" s="11"/>
-      <c r="M316" s="11"/>
-      <c r="N316" s="12"/>
-    </row>
-    <row r="317" spans="1:14">
-      <c r="A317" s="8"/>
-      <c r="B317" s="9"/>
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="F317" s="9"/>
-      <c r="G317" s="9"/>
-      <c r="H317" s="9"/>
-      <c r="I317" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J317" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K317" s="11"/>
-      <c r="L317" s="11"/>
-      <c r="M317" s="11"/>
-      <c r="N317" s="12"/>
-    </row>
-    <row r="318" spans="1:14">
-      <c r="A318" s="8"/>
-      <c r="B318" s="9"/>
-      <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="F318" s="9"/>
-      <c r="G318" s="9"/>
-      <c r="H318" s="9"/>
-      <c r="I318" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J318" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K318" s="11"/>
-      <c r="L318" s="11"/>
-      <c r="M318" s="11"/>
-      <c r="N318" s="12"/>
-    </row>
-    <row r="319" spans="1:14">
-      <c r="A319" s="8"/>
-      <c r="B319" s="9"/>
-      <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="F319" s="9"/>
-      <c r="G319" s="9"/>
-      <c r="H319" s="9"/>
-      <c r="I319" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J319" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K319" s="11"/>
-      <c r="L319" s="11"/>
-      <c r="M319" s="11"/>
-      <c r="N319" s="12"/>
-    </row>
-    <row r="320" spans="1:14">
-      <c r="A320" s="8"/>
-      <c r="B320" s="9"/>
-      <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="F320" s="9"/>
-      <c r="G320" s="9"/>
-      <c r="H320" s="9"/>
-      <c r="I320" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J320" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K320" s="11"/>
-      <c r="L320" s="11"/>
-      <c r="M320" s="11"/>
-      <c r="N320" s="12"/>
-    </row>
-    <row r="321" spans="1:14">
-      <c r="A321" s="8"/>
-      <c r="B321" s="9"/>
-      <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="F321" s="9"/>
-      <c r="G321" s="9"/>
-      <c r="H321" s="9"/>
-      <c r="I321" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J321" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K321" s="11"/>
-      <c r="L321" s="11"/>
-      <c r="M321" s="11"/>
-      <c r="N321" s="12"/>
-    </row>
-    <row r="322" spans="1:14">
-      <c r="A322" s="8"/>
-      <c r="B322" s="9"/>
-      <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="F322" s="9"/>
-      <c r="G322" s="9"/>
-      <c r="H322" s="9"/>
-      <c r="I322" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J322" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K322" s="11"/>
-      <c r="L322" s="11"/>
-      <c r="M322" s="11"/>
-      <c r="N322" s="12"/>
-    </row>
-    <row r="323" spans="1:14">
-      <c r="A323" s="8"/>
-      <c r="B323" s="9"/>
-      <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="F323" s="9"/>
-      <c r="G323" s="9"/>
-      <c r="H323" s="9"/>
-      <c r="I323" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J323" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K323" s="11"/>
-      <c r="L323" s="11"/>
-      <c r="M323" s="11"/>
-      <c r="N323" s="12"/>
-    </row>
-    <row r="324" spans="1:14">
-      <c r="A324" s="8"/>
-      <c r="B324" s="9"/>
-      <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="F324" s="9"/>
-      <c r="G324" s="9"/>
-      <c r="H324" s="9"/>
-      <c r="I324" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J324" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K324" s="11"/>
-      <c r="L324" s="11"/>
-      <c r="M324" s="11"/>
-      <c r="N324" s="12"/>
-    </row>
-    <row r="325" spans="1:14">
-      <c r="A325" s="8"/>
-      <c r="B325" s="9"/>
-      <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="F325" s="9"/>
-      <c r="G325" s="9"/>
-      <c r="H325" s="9"/>
-      <c r="I325" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J325" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K325" s="11"/>
-      <c r="L325" s="11"/>
-      <c r="M325" s="11"/>
-      <c r="N325" s="12"/>
-    </row>
-    <row r="326" spans="1:14">
-      <c r="A326" s="8"/>
-      <c r="B326" s="9"/>
-      <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="F326" s="9"/>
-      <c r="G326" s="9"/>
-      <c r="H326" s="9"/>
-      <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I381" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
-        <v/>
-      </c>
-      <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J381" si="15">IF(I326="","",1440-I326)</f>
-        <v/>
-      </c>
-      <c r="K326" s="11"/>
-      <c r="L326" s="11"/>
-      <c r="M326" s="11"/>
-      <c r="N326" s="12"/>
-    </row>
-    <row r="327" spans="1:14">
-      <c r="A327" s="8"/>
-      <c r="B327" s="9"/>
-      <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="F327" s="9"/>
-      <c r="G327" s="9"/>
-      <c r="H327" s="9"/>
-      <c r="I327" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J327" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K327" s="11"/>
-      <c r="L327" s="11"/>
-      <c r="M327" s="11"/>
-      <c r="N327" s="12"/>
-    </row>
-    <row r="328" spans="1:14">
-      <c r="A328" s="8"/>
-      <c r="B328" s="9"/>
-      <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="F328" s="9"/>
-      <c r="G328" s="9"/>
-      <c r="H328" s="9"/>
-      <c r="I328" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J328" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K328" s="11"/>
-      <c r="L328" s="11"/>
-      <c r="M328" s="11"/>
-      <c r="N328" s="12"/>
-    </row>
-    <row r="329" spans="1:14">
-      <c r="A329" s="8"/>
-      <c r="B329" s="9"/>
-      <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="F329" s="9"/>
-      <c r="G329" s="9"/>
-      <c r="H329" s="9"/>
-      <c r="I329" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J329" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K329" s="11"/>
-      <c r="L329" s="11"/>
-      <c r="M329" s="11"/>
-      <c r="N329" s="12"/>
-    </row>
-    <row r="330" spans="1:14">
-      <c r="A330" s="8"/>
-      <c r="B330" s="9"/>
-      <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="F330" s="9"/>
-      <c r="G330" s="9"/>
-      <c r="H330" s="9"/>
-      <c r="I330" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J330" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K330" s="11"/>
-      <c r="L330" s="11"/>
-      <c r="M330" s="11"/>
-      <c r="N330" s="12"/>
-    </row>
-    <row r="331" spans="1:14">
-      <c r="A331" s="8"/>
-      <c r="B331" s="9"/>
-      <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="F331" s="9"/>
-      <c r="G331" s="9"/>
-      <c r="H331" s="9"/>
-      <c r="I331" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J331" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K331" s="11"/>
-      <c r="L331" s="11"/>
-      <c r="M331" s="11"/>
-      <c r="N331" s="12"/>
-    </row>
-    <row r="332" spans="1:14">
-      <c r="A332" s="8"/>
-      <c r="B332" s="9"/>
-      <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="F332" s="9"/>
-      <c r="G332" s="9"/>
-      <c r="H332" s="9"/>
-      <c r="I332" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J332" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K332" s="11"/>
-      <c r="L332" s="11"/>
-      <c r="M332" s="11"/>
-      <c r="N332" s="12"/>
-    </row>
-    <row r="333" spans="1:14">
-      <c r="A333" s="8"/>
-      <c r="B333" s="9"/>
-      <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="F333" s="9"/>
-      <c r="G333" s="9"/>
-      <c r="H333" s="9"/>
-      <c r="I333" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J333" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K333" s="11"/>
-      <c r="L333" s="11"/>
-      <c r="M333" s="11"/>
-      <c r="N333" s="12"/>
-    </row>
-    <row r="334" spans="1:14">
-      <c r="A334" s="8"/>
-      <c r="B334" s="9"/>
-      <c r="C334" s="9"/>
-      <c r="D334" s="9"/>
-      <c r="E334" s="9"/>
-      <c r="F334" s="9"/>
-      <c r="G334" s="9"/>
-      <c r="H334" s="9"/>
-      <c r="I334" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J334" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K334" s="11"/>
-      <c r="L334" s="11"/>
-      <c r="M334" s="11"/>
-      <c r="N334" s="12"/>
-    </row>
-    <row r="335" spans="1:14">
-      <c r="A335" s="8"/>
-      <c r="B335" s="9"/>
-      <c r="C335" s="9"/>
-      <c r="D335" s="9"/>
-      <c r="E335" s="9"/>
-      <c r="F335" s="9"/>
-      <c r="G335" s="9"/>
-      <c r="H335" s="9"/>
-      <c r="I335" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J335" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K335" s="11"/>
-      <c r="L335" s="11"/>
-      <c r="M335" s="11"/>
-      <c r="N335" s="12"/>
-    </row>
-    <row r="336" spans="1:14">
-      <c r="A336" s="8"/>
-      <c r="B336" s="9"/>
-      <c r="C336" s="9"/>
-      <c r="D336" s="9"/>
-      <c r="E336" s="9"/>
-      <c r="F336" s="9"/>
-      <c r="G336" s="9"/>
-      <c r="H336" s="9"/>
-      <c r="I336" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J336" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K336" s="11"/>
-      <c r="L336" s="11"/>
-      <c r="M336" s="11"/>
-      <c r="N336" s="12"/>
-    </row>
-    <row r="337" spans="1:14">
-      <c r="A337" s="8"/>
-      <c r="B337" s="9"/>
-      <c r="C337" s="9"/>
-      <c r="D337" s="9"/>
-      <c r="E337" s="9"/>
-      <c r="F337" s="9"/>
-      <c r="G337" s="9"/>
-      <c r="H337" s="9"/>
-      <c r="I337" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J337" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K337" s="11"/>
-      <c r="L337" s="11"/>
-      <c r="M337" s="11"/>
-      <c r="N337" s="12"/>
-    </row>
-    <row r="338" spans="1:14">
-      <c r="A338" s="8"/>
-      <c r="B338" s="9"/>
-      <c r="C338" s="9"/>
-      <c r="D338" s="9"/>
-      <c r="E338" s="9"/>
-      <c r="F338" s="9"/>
-      <c r="G338" s="9"/>
-      <c r="H338" s="9"/>
-      <c r="I338" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J338" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K338" s="11"/>
-      <c r="L338" s="11"/>
-      <c r="M338" s="11"/>
-      <c r="N338" s="12"/>
-    </row>
-    <row r="339" spans="1:14">
-      <c r="A339" s="8"/>
-      <c r="B339" s="9"/>
-      <c r="C339" s="9"/>
-      <c r="D339" s="9"/>
-      <c r="E339" s="9"/>
-      <c r="F339" s="9"/>
-      <c r="G339" s="9"/>
-      <c r="H339" s="9"/>
-      <c r="I339" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J339" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K339" s="11"/>
-      <c r="L339" s="11"/>
-      <c r="M339" s="11"/>
-      <c r="N339" s="12"/>
-    </row>
-    <row r="340" spans="1:14">
-      <c r="A340" s="8"/>
-      <c r="B340" s="9"/>
-      <c r="C340" s="9"/>
-      <c r="D340" s="9"/>
-      <c r="E340" s="9"/>
-      <c r="F340" s="9"/>
-      <c r="G340" s="9"/>
-      <c r="H340" s="9"/>
-      <c r="I340" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J340" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K340" s="11"/>
-      <c r="L340" s="11"/>
-      <c r="M340" s="11"/>
-      <c r="N340" s="12"/>
-    </row>
-    <row r="341" spans="1:14">
-      <c r="A341" s="8"/>
-      <c r="B341" s="9"/>
-      <c r="C341" s="9"/>
-      <c r="D341" s="9"/>
-      <c r="E341" s="9"/>
-      <c r="F341" s="9"/>
-      <c r="G341" s="9"/>
-      <c r="H341" s="9"/>
-      <c r="I341" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J341" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K341" s="11"/>
-      <c r="L341" s="11"/>
-      <c r="M341" s="11"/>
-      <c r="N341" s="12"/>
-    </row>
-    <row r="342" spans="1:14">
-      <c r="A342" s="8"/>
-      <c r="B342" s="9"/>
-      <c r="C342" s="9"/>
-      <c r="D342" s="9"/>
-      <c r="E342" s="9"/>
-      <c r="F342" s="9"/>
-      <c r="G342" s="9"/>
-      <c r="H342" s="9"/>
-      <c r="I342" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J342" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K342" s="11"/>
-      <c r="L342" s="11"/>
-      <c r="M342" s="11"/>
-      <c r="N342" s="12"/>
-    </row>
-    <row r="343" spans="1:14">
-      <c r="A343" s="8"/>
-      <c r="B343" s="9"/>
-      <c r="C343" s="9"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="F343" s="9"/>
-      <c r="G343" s="9"/>
-      <c r="H343" s="9"/>
-      <c r="I343" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J343" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K343" s="11"/>
-      <c r="L343" s="11"/>
-      <c r="M343" s="11"/>
-      <c r="N343" s="12"/>
-    </row>
-    <row r="344" spans="1:14">
-      <c r="A344" s="8"/>
-      <c r="B344" s="9"/>
-      <c r="C344" s="9"/>
-      <c r="D344" s="9"/>
-      <c r="E344" s="9"/>
-      <c r="F344" s="9"/>
-      <c r="G344" s="9"/>
-      <c r="H344" s="9"/>
-      <c r="I344" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J344" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K344" s="11"/>
-      <c r="L344" s="11"/>
-      <c r="M344" s="11"/>
-      <c r="N344" s="12"/>
-    </row>
-    <row r="345" spans="1:14">
-      <c r="A345" s="8"/>
-      <c r="B345" s="9"/>
-      <c r="C345" s="9"/>
-      <c r="D345" s="9"/>
-      <c r="E345" s="9"/>
-      <c r="F345" s="9"/>
-      <c r="G345" s="9"/>
-      <c r="H345" s="9"/>
-      <c r="I345" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J345" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K345" s="11"/>
-      <c r="L345" s="11"/>
-      <c r="M345" s="11"/>
-      <c r="N345" s="12"/>
-    </row>
-    <row r="346" spans="1:14">
-      <c r="A346" s="8"/>
-      <c r="B346" s="9"/>
-      <c r="C346" s="9"/>
-      <c r="D346" s="9"/>
-      <c r="E346" s="9"/>
-      <c r="F346" s="9"/>
-      <c r="G346" s="9"/>
-      <c r="H346" s="9"/>
-      <c r="I346" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J346" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K346" s="11"/>
-      <c r="L346" s="11"/>
-      <c r="M346" s="11"/>
-      <c r="N346" s="12"/>
-    </row>
-    <row r="347" spans="1:14">
-      <c r="A347" s="8"/>
-      <c r="B347" s="9"/>
-      <c r="C347" s="9"/>
-      <c r="D347" s="9"/>
-      <c r="E347" s="9"/>
-      <c r="F347" s="9"/>
-      <c r="G347" s="9"/>
-      <c r="H347" s="9"/>
-      <c r="I347" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J347" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K347" s="11"/>
-      <c r="L347" s="11"/>
-      <c r="M347" s="11"/>
-      <c r="N347" s="12"/>
-    </row>
-    <row r="348" spans="1:14">
-      <c r="A348" s="8"/>
-      <c r="B348" s="9"/>
-      <c r="C348" s="9"/>
-      <c r="D348" s="9"/>
-      <c r="E348" s="9"/>
-      <c r="F348" s="9"/>
-      <c r="G348" s="9"/>
-      <c r="H348" s="9"/>
-      <c r="I348" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J348" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K348" s="11"/>
-      <c r="L348" s="11"/>
-      <c r="M348" s="11"/>
-      <c r="N348" s="12"/>
-    </row>
-    <row r="349" spans="1:14">
-      <c r="A349" s="8"/>
-      <c r="B349" s="9"/>
-      <c r="C349" s="9"/>
-      <c r="D349" s="9"/>
-      <c r="E349" s="9"/>
-      <c r="F349" s="9"/>
-      <c r="G349" s="9"/>
-      <c r="H349" s="9"/>
-      <c r="I349" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J349" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K349" s="11"/>
-      <c r="L349" s="11"/>
-      <c r="M349" s="11"/>
-      <c r="N349" s="12"/>
-    </row>
-    <row r="350" spans="1:14">
-      <c r="A350" s="8"/>
-      <c r="B350" s="9"/>
-      <c r="C350" s="9"/>
-      <c r="D350" s="9"/>
-      <c r="E350" s="9"/>
-      <c r="F350" s="9"/>
-      <c r="G350" s="9"/>
-      <c r="H350" s="9"/>
-      <c r="I350" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J350" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K350" s="11"/>
-      <c r="L350" s="11"/>
-      <c r="M350" s="11"/>
-      <c r="N350" s="12"/>
-    </row>
-    <row r="351" spans="1:14">
-      <c r="A351" s="8"/>
-      <c r="B351" s="9"/>
-      <c r="C351" s="9"/>
-      <c r="D351" s="9"/>
-      <c r="E351" s="9"/>
-      <c r="F351" s="9"/>
-      <c r="G351" s="9"/>
-      <c r="H351" s="9"/>
-      <c r="I351" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J351" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K351" s="11"/>
-      <c r="L351" s="11"/>
-      <c r="M351" s="11"/>
-      <c r="N351" s="12"/>
-    </row>
-    <row r="352" spans="1:14">
-      <c r="A352" s="8"/>
-      <c r="B352" s="9"/>
-      <c r="C352" s="9"/>
-      <c r="D352" s="9"/>
-      <c r="E352" s="9"/>
-      <c r="F352" s="9"/>
-      <c r="G352" s="9"/>
-      <c r="H352" s="9"/>
-      <c r="I352" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J352" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K352" s="11"/>
-      <c r="L352" s="11"/>
-      <c r="M352" s="11"/>
-      <c r="N352" s="12"/>
-    </row>
-    <row r="353" spans="1:14">
-      <c r="A353" s="8"/>
-      <c r="B353" s="9"/>
-      <c r="C353" s="9"/>
-      <c r="D353" s="9"/>
-      <c r="E353" s="9"/>
-      <c r="F353" s="9"/>
-      <c r="G353" s="9"/>
-      <c r="H353" s="9"/>
-      <c r="I353" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J353" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K353" s="11"/>
-      <c r="L353" s="11"/>
-      <c r="M353" s="11"/>
-      <c r="N353" s="12"/>
-    </row>
-    <row r="354" spans="1:14">
-      <c r="A354" s="8"/>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
-      <c r="I354" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J354" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K354" s="11"/>
-      <c r="L354" s="11"/>
-      <c r="M354" s="11"/>
-      <c r="N354" s="12"/>
-    </row>
-    <row r="355" spans="1:14">
-      <c r="A355" s="8"/>
-      <c r="B355" s="9"/>
-      <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="F355" s="9"/>
-      <c r="G355" s="9"/>
-      <c r="H355" s="9"/>
-      <c r="I355" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J355" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K355" s="11"/>
-      <c r="L355" s="11"/>
-      <c r="M355" s="11"/>
-      <c r="N355" s="12"/>
-    </row>
-    <row r="356" spans="1:14">
-      <c r="A356" s="8"/>
-      <c r="B356" s="9"/>
-      <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="F356" s="9"/>
-      <c r="G356" s="9"/>
-      <c r="H356" s="9"/>
-      <c r="I356" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J356" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K356" s="11"/>
-      <c r="L356" s="11"/>
-      <c r="M356" s="11"/>
-      <c r="N356" s="12"/>
-    </row>
-    <row r="357" spans="1:14">
-      <c r="A357" s="8"/>
-      <c r="B357" s="9"/>
-      <c r="C357" s="9"/>
-      <c r="D357" s="9"/>
-      <c r="E357" s="9"/>
-      <c r="F357" s="9"/>
-      <c r="G357" s="9"/>
-      <c r="H357" s="9"/>
-      <c r="I357" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J357" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K357" s="11"/>
-      <c r="L357" s="11"/>
-      <c r="M357" s="11"/>
-      <c r="N357" s="12"/>
-    </row>
-    <row r="358" spans="1:14">
-      <c r="A358" s="8"/>
-      <c r="B358" s="9"/>
-      <c r="C358" s="9"/>
-      <c r="D358" s="9"/>
-      <c r="E358" s="9"/>
-      <c r="F358" s="9"/>
-      <c r="G358" s="9"/>
-      <c r="H358" s="9"/>
-      <c r="I358" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J358" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K358" s="11"/>
-      <c r="L358" s="11"/>
-      <c r="M358" s="11"/>
-      <c r="N358" s="12"/>
-    </row>
-    <row r="359" spans="1:14">
-      <c r="A359" s="8"/>
-      <c r="B359" s="9"/>
-      <c r="C359" s="9"/>
-      <c r="D359" s="9"/>
-      <c r="E359" s="9"/>
-      <c r="F359" s="9"/>
-      <c r="G359" s="9"/>
-      <c r="H359" s="9"/>
-      <c r="I359" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J359" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K359" s="11"/>
-      <c r="L359" s="11"/>
-      <c r="M359" s="11"/>
-      <c r="N359" s="12"/>
-    </row>
-    <row r="360" spans="1:14">
-      <c r="A360" s="8"/>
-      <c r="B360" s="9"/>
-      <c r="C360" s="9"/>
-      <c r="D360" s="9"/>
-      <c r="E360" s="9"/>
-      <c r="F360" s="9"/>
-      <c r="G360" s="9"/>
-      <c r="H360" s="9"/>
-      <c r="I360" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J360" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K360" s="11"/>
-      <c r="L360" s="11"/>
-      <c r="M360" s="11"/>
-      <c r="N360" s="12"/>
-    </row>
-    <row r="361" spans="1:14">
-      <c r="A361" s="8"/>
-      <c r="B361" s="9"/>
-      <c r="C361" s="9"/>
-      <c r="D361" s="9"/>
-      <c r="E361" s="9"/>
-      <c r="F361" s="9"/>
-      <c r="G361" s="9"/>
-      <c r="H361" s="9"/>
-      <c r="I361" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J361" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K361" s="11"/>
-      <c r="L361" s="11"/>
-      <c r="M361" s="11"/>
-      <c r="N361" s="12"/>
-    </row>
-    <row r="362" spans="1:14">
-      <c r="A362" s="8"/>
-      <c r="B362" s="9"/>
-      <c r="C362" s="9"/>
-      <c r="D362" s="9"/>
-      <c r="E362" s="9"/>
-      <c r="F362" s="9"/>
-      <c r="G362" s="9"/>
-      <c r="H362" s="9"/>
-      <c r="I362" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J362" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K362" s="11"/>
-      <c r="L362" s="11"/>
-      <c r="M362" s="11"/>
-      <c r="N362" s="12"/>
-    </row>
-    <row r="363" spans="1:14">
-      <c r="A363" s="8"/>
-      <c r="B363" s="9"/>
-      <c r="C363" s="9"/>
-      <c r="D363" s="9"/>
-      <c r="E363" s="9"/>
-      <c r="F363" s="9"/>
-      <c r="G363" s="9"/>
-      <c r="H363" s="9"/>
-      <c r="I363" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J363" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K363" s="11"/>
-      <c r="L363" s="11"/>
-      <c r="M363" s="11"/>
-      <c r="N363" s="12"/>
-    </row>
-    <row r="364" spans="1:14">
-      <c r="A364" s="8"/>
-      <c r="B364" s="9"/>
-      <c r="C364" s="9"/>
-      <c r="D364" s="9"/>
-      <c r="E364" s="9"/>
-      <c r="F364" s="9"/>
-      <c r="G364" s="9"/>
-      <c r="H364" s="9"/>
-      <c r="I364" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J364" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K364" s="11"/>
-      <c r="L364" s="11"/>
-      <c r="M364" s="11"/>
-      <c r="N364" s="12"/>
-    </row>
-    <row r="365" spans="1:14">
-      <c r="A365" s="8"/>
-      <c r="B365" s="9"/>
-      <c r="C365" s="9"/>
-      <c r="D365" s="9"/>
-      <c r="E365" s="9"/>
-      <c r="F365" s="9"/>
-      <c r="G365" s="9"/>
-      <c r="H365" s="9"/>
-      <c r="I365" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J365" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K365" s="11"/>
-      <c r="L365" s="11"/>
-      <c r="M365" s="11"/>
-      <c r="N365" s="12"/>
-    </row>
-    <row r="366" spans="1:14">
-      <c r="A366" s="8"/>
-      <c r="B366" s="9"/>
-      <c r="C366" s="9"/>
-      <c r="D366" s="9"/>
-      <c r="E366" s="9"/>
-      <c r="F366" s="9"/>
-      <c r="G366" s="9"/>
-      <c r="H366" s="9"/>
-      <c r="I366" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J366" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K366" s="11"/>
-      <c r="L366" s="11"/>
-      <c r="M366" s="11"/>
-      <c r="N366" s="12"/>
-    </row>
-    <row r="367" spans="1:14">
-      <c r="A367" s="8"/>
-      <c r="B367" s="9"/>
-      <c r="C367" s="9"/>
-      <c r="D367" s="9"/>
-      <c r="E367" s="9"/>
-      <c r="F367" s="9"/>
-      <c r="G367" s="9"/>
-      <c r="H367" s="9"/>
-      <c r="I367" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J367" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K367" s="11"/>
-      <c r="L367" s="11"/>
-      <c r="M367" s="11"/>
-      <c r="N367" s="12"/>
-    </row>
-    <row r="368" spans="1:14">
-      <c r="A368" s="8"/>
-      <c r="B368" s="9"/>
-      <c r="C368" s="9"/>
-      <c r="D368" s="9"/>
-      <c r="E368" s="9"/>
-      <c r="F368" s="9"/>
-      <c r="G368" s="9"/>
-      <c r="H368" s="9"/>
-      <c r="I368" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J368" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K368" s="11"/>
-      <c r="L368" s="11"/>
-      <c r="M368" s="11"/>
-      <c r="N368" s="12"/>
-    </row>
-    <row r="369" spans="1:14">
-      <c r="A369" s="8"/>
-      <c r="B369" s="9"/>
-      <c r="C369" s="9"/>
-      <c r="D369" s="9"/>
-      <c r="E369" s="9"/>
-      <c r="F369" s="9"/>
-      <c r="G369" s="9"/>
-      <c r="H369" s="9"/>
-      <c r="I369" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J369" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K369" s="11"/>
-      <c r="L369" s="11"/>
-      <c r="M369" s="11"/>
-      <c r="N369" s="12"/>
-    </row>
-    <row r="370" spans="1:14">
-      <c r="A370" s="8"/>
-      <c r="B370" s="9"/>
-      <c r="C370" s="9"/>
-      <c r="D370" s="9"/>
-      <c r="E370" s="9"/>
-      <c r="F370" s="9"/>
-      <c r="G370" s="9"/>
-      <c r="H370" s="9"/>
-      <c r="I370" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J370" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K370" s="11"/>
-      <c r="L370" s="11"/>
-      <c r="M370" s="11"/>
-      <c r="N370" s="12"/>
-    </row>
-    <row r="371" spans="1:14">
-      <c r="A371" s="8"/>
-      <c r="B371" s="9"/>
-      <c r="C371" s="9"/>
-      <c r="D371" s="9"/>
-      <c r="E371" s="9"/>
-      <c r="F371" s="9"/>
-      <c r="G371" s="9"/>
-      <c r="H371" s="9"/>
-      <c r="I371" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J371" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K371" s="11"/>
-      <c r="L371" s="11"/>
-      <c r="M371" s="11"/>
-      <c r="N371" s="12"/>
-    </row>
-    <row r="372" spans="1:14">
-      <c r="A372" s="8"/>
-      <c r="B372" s="9"/>
-      <c r="C372" s="9"/>
-      <c r="D372" s="9"/>
-      <c r="E372" s="9"/>
-      <c r="F372" s="9"/>
-      <c r="G372" s="9"/>
-      <c r="H372" s="9"/>
-      <c r="I372" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J372" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K372" s="11"/>
-      <c r="L372" s="11"/>
-      <c r="M372" s="11"/>
-      <c r="N372" s="12"/>
-    </row>
-    <row r="373" spans="1:14">
-      <c r="A373" s="8"/>
-      <c r="B373" s="9"/>
-      <c r="C373" s="9"/>
-      <c r="D373" s="9"/>
-      <c r="E373" s="9"/>
-      <c r="F373" s="9"/>
-      <c r="G373" s="9"/>
-      <c r="H373" s="9"/>
-      <c r="I373" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J373" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K373" s="11"/>
-      <c r="L373" s="11"/>
-      <c r="M373" s="11"/>
-      <c r="N373" s="12"/>
-    </row>
-    <row r="374" spans="1:14">
-      <c r="A374" s="8"/>
-      <c r="B374" s="9"/>
-      <c r="C374" s="9"/>
-      <c r="D374" s="9"/>
-      <c r="E374" s="9"/>
-      <c r="F374" s="9"/>
-      <c r="G374" s="9"/>
-      <c r="H374" s="9"/>
-      <c r="I374" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J374" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K374" s="11"/>
-      <c r="L374" s="11"/>
-      <c r="M374" s="11"/>
-      <c r="N374" s="12"/>
-    </row>
-    <row r="375" spans="1:14">
-      <c r="A375" s="8"/>
-      <c r="B375" s="9"/>
-      <c r="C375" s="9"/>
-      <c r="D375" s="9"/>
-      <c r="E375" s="9"/>
-      <c r="F375" s="9"/>
-      <c r="G375" s="9"/>
-      <c r="H375" s="9"/>
-      <c r="I375" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J375" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K375" s="11"/>
-      <c r="L375" s="11"/>
-      <c r="M375" s="11"/>
-      <c r="N375" s="12"/>
-    </row>
-    <row r="376" spans="1:14">
-      <c r="A376" s="8"/>
-      <c r="B376" s="9"/>
-      <c r="C376" s="9"/>
-      <c r="D376" s="9"/>
-      <c r="E376" s="9"/>
-      <c r="F376" s="9"/>
-      <c r="G376" s="9"/>
-      <c r="H376" s="9"/>
-      <c r="I376" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J376" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K376" s="11"/>
-      <c r="L376" s="11"/>
-      <c r="M376" s="11"/>
-      <c r="N376" s="12"/>
-    </row>
-    <row r="377" spans="1:14">
-      <c r="A377" s="8"/>
-      <c r="B377" s="9"/>
-      <c r="C377" s="9"/>
-      <c r="D377" s="9"/>
-      <c r="E377" s="9"/>
-      <c r="F377" s="9"/>
-      <c r="G377" s="9"/>
-      <c r="H377" s="9"/>
-      <c r="I377" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J377" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K377" s="11"/>
-      <c r="L377" s="11"/>
-      <c r="M377" s="11"/>
-      <c r="N377" s="12"/>
-    </row>
-    <row r="378" spans="1:14">
-      <c r="A378" s="8"/>
-      <c r="B378" s="9"/>
-      <c r="C378" s="9"/>
-      <c r="D378" s="9"/>
-      <c r="E378" s="9"/>
-      <c r="F378" s="9"/>
-      <c r="G378" s="9"/>
-      <c r="H378" s="9"/>
-      <c r="I378" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J378" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K378" s="11"/>
-      <c r="L378" s="11"/>
-      <c r="M378" s="11"/>
-      <c r="N378" s="12"/>
-    </row>
-    <row r="379" spans="1:14">
-      <c r="A379" s="8"/>
-      <c r="B379" s="9"/>
-      <c r="C379" s="9"/>
-      <c r="D379" s="9"/>
-      <c r="E379" s="9"/>
-      <c r="F379" s="9"/>
-      <c r="G379" s="9"/>
-      <c r="H379" s="9"/>
-      <c r="I379" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J379" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K379" s="11"/>
-      <c r="L379" s="11"/>
-      <c r="M379" s="11"/>
-      <c r="N379" s="12"/>
-    </row>
-    <row r="380" spans="1:14">
-      <c r="A380" s="8"/>
-      <c r="B380" s="9"/>
-      <c r="C380" s="9"/>
-      <c r="D380" s="9"/>
-      <c r="E380" s="9"/>
-      <c r="F380" s="9"/>
-      <c r="G380" s="9"/>
-      <c r="H380" s="9"/>
-      <c r="I380" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J380" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K380" s="11"/>
-      <c r="L380" s="11"/>
-      <c r="M380" s="11"/>
-      <c r="N380" s="12"/>
-    </row>
-    <row r="381" spans="1:14">
-      <c r="A381" s="8"/>
-      <c r="B381" s="9"/>
-      <c r="C381" s="9"/>
-      <c r="D381" s="9"/>
-      <c r="E381" s="9"/>
-      <c r="F381" s="9"/>
-      <c r="G381" s="9"/>
-      <c r="H381" s="9"/>
-      <c r="I381" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J381" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K381" s="11"/>
-      <c r="L381" s="11"/>
-      <c r="M381" s="11"/>
-      <c r="N381" s="12"/>
-    </row>
-    <row r="382" spans="1:14">
-      <c r="A382" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:G3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="J6:J381">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J26">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J26">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M381">
-      <formula1>"High,Medium,Low"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L381">
-      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K381">
-      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>